--- a/AC_2018/AC_032_032-Husnabad.xlsx
+++ b/AC_2018/AC_032_032-Husnabad.xlsx
@@ -17,7 +17,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="5">
+  <fonts count="6">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -45,6 +45,11 @@
       <b val="1"/>
       <color rgb="00000000"/>
       <sz val="11"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <sz val="10"/>
     </font>
   </fonts>
   <fills count="6">
@@ -79,7 +84,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="5">
+  <borders count="6">
     <border>
       <left/>
       <right/>
@@ -143,11 +148,19 @@
         <color rgb="001B365D"/>
       </bottom>
     </border>
+    <border>
+      <top style="thin">
+        <color rgb="00D9D9D9"/>
+      </top>
+      <bottom style="double">
+        <color rgb="00000000"/>
+      </bottom>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="25">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -184,6 +197,23 @@
     <xf numFmtId="0" fontId="4" fillId="5" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="3" fontId="4" fillId="5" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="3" fontId="5" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="3" fontId="5" fillId="4" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
   </cellXfs>
@@ -794,10 +824,10 @@
         <v>12</v>
       </c>
       <c r="U6" s="5" t="n">
-        <v>727</v>
+        <v>0</v>
       </c>
       <c r="V6" s="5" t="n">
-        <v>2157</v>
+        <v>1442</v>
       </c>
       <c r="W6" s="5" t="n">
         <v>0</v>
@@ -871,10 +901,10 @@
         <v>29</v>
       </c>
       <c r="U7" s="5" t="n">
-        <v>793</v>
+        <v>0</v>
       </c>
       <c r="V7" s="5" t="n">
-        <v>2321</v>
+        <v>1557</v>
       </c>
       <c r="W7" s="5" t="n">
         <v>0</v>
@@ -948,10 +978,10 @@
         <v>14</v>
       </c>
       <c r="U8" s="5" t="n">
-        <v>525</v>
+        <v>0</v>
       </c>
       <c r="V8" s="5" t="n">
-        <v>1547</v>
+        <v>1036</v>
       </c>
       <c r="W8" s="5" t="n">
         <v>0</v>
@@ -1025,10 +1055,10 @@
         <v>16</v>
       </c>
       <c r="U9" s="5" t="n">
-        <v>813</v>
+        <v>0</v>
       </c>
       <c r="V9" s="5" t="n">
-        <v>2407</v>
+        <v>1610</v>
       </c>
       <c r="W9" s="5" t="n">
         <v>0</v>
@@ -1102,10 +1132,10 @@
         <v>14</v>
       </c>
       <c r="U10" s="5" t="n">
-        <v>863</v>
+        <v>0</v>
       </c>
       <c r="V10" s="5" t="n">
-        <v>2554</v>
+        <v>1705</v>
       </c>
       <c r="W10" s="5" t="n">
         <v>0</v>
@@ -1179,10 +1209,10 @@
         <v>13</v>
       </c>
       <c r="U11" s="5" t="n">
-        <v>628</v>
+        <v>0</v>
       </c>
       <c r="V11" s="5" t="n">
-        <v>1857</v>
+        <v>1242</v>
       </c>
       <c r="W11" s="5" t="n">
         <v>0</v>
@@ -1256,10 +1286,10 @@
         <v>9</v>
       </c>
       <c r="U12" s="5" t="n">
-        <v>725</v>
+        <v>0</v>
       </c>
       <c r="V12" s="5" t="n">
-        <v>2157</v>
+        <v>1441</v>
       </c>
       <c r="W12" s="5" t="n">
         <v>0</v>
@@ -1333,10 +1363,10 @@
         <v>20</v>
       </c>
       <c r="U13" s="5" t="n">
-        <v>736</v>
+        <v>0</v>
       </c>
       <c r="V13" s="5" t="n">
-        <v>2167</v>
+        <v>1451</v>
       </c>
       <c r="W13" s="5" t="n">
         <v>0</v>
@@ -1410,10 +1440,10 @@
         <v>23</v>
       </c>
       <c r="U14" s="5" t="n">
-        <v>1108</v>
+        <v>0</v>
       </c>
       <c r="V14" s="5" t="n">
-        <v>1</v>
+        <v>2193</v>
       </c>
       <c r="W14" s="5" t="n">
         <v>0</v>
@@ -1489,10 +1519,10 @@
         <v>20</v>
       </c>
       <c r="U15" s="5" t="n">
-        <v>1123</v>
+        <v>0</v>
       </c>
       <c r="V15" s="5" t="n">
-        <v>3329</v>
+        <v>2226</v>
       </c>
       <c r="W15" s="5" t="n">
         <v>0</v>
@@ -1566,10 +1596,10 @@
         <v>20</v>
       </c>
       <c r="U16" s="5" t="n">
-        <v>790</v>
+        <v>0</v>
       </c>
       <c r="V16" s="5" t="n">
-        <v>2336</v>
+        <v>1566</v>
       </c>
       <c r="W16" s="5" t="n">
         <v>4</v>
@@ -1643,10 +1673,10 @@
         <v>17</v>
       </c>
       <c r="U17" s="5" t="n">
-        <v>840</v>
+        <v>0</v>
       </c>
       <c r="V17" s="5" t="n">
-        <v>2486</v>
+        <v>1663</v>
       </c>
       <c r="W17" s="5" t="n">
         <v>4</v>
@@ -1720,10 +1750,10 @@
         <v>11</v>
       </c>
       <c r="U18" s="5" t="n">
-        <v>503</v>
+        <v>0</v>
       </c>
       <c r="V18" s="5" t="n">
-        <v>1487</v>
+        <v>995</v>
       </c>
       <c r="W18" s="5" t="n">
         <v>0</v>
@@ -1797,10 +1827,10 @@
         <v>18</v>
       </c>
       <c r="U19" s="5" t="n">
-        <v>806</v>
+        <v>0</v>
       </c>
       <c r="V19" s="5" t="n">
-        <v>2382</v>
+        <v>1594</v>
       </c>
       <c r="W19" s="5" t="n">
         <v>4</v>
@@ -1874,10 +1904,10 @@
         <v>13</v>
       </c>
       <c r="U20" s="5" t="n">
-        <v>556</v>
+        <v>0</v>
       </c>
       <c r="V20" s="5" t="n">
-        <v>1643</v>
+        <v>1100</v>
       </c>
       <c r="W20" s="5" t="n">
         <v>4</v>
@@ -1951,10 +1981,10 @@
         <v>13</v>
       </c>
       <c r="U21" s="5" t="n">
-        <v>832</v>
+        <v>0</v>
       </c>
       <c r="V21" s="5" t="n">
-        <v>2473</v>
+        <v>1654</v>
       </c>
       <c r="W21" s="5" t="n">
         <v>4</v>
@@ -2028,10 +2058,10 @@
         <v>8</v>
       </c>
       <c r="U22" s="5" t="n">
-        <v>680</v>
+        <v>0</v>
       </c>
       <c r="V22" s="5" t="n">
-        <v>2024</v>
+        <v>1352</v>
       </c>
       <c r="W22" s="5" t="n">
         <v>4</v>
@@ -2105,10 +2135,10 @@
         <v>14</v>
       </c>
       <c r="U23" s="5" t="n">
-        <v>743</v>
+        <v>0</v>
       </c>
       <c r="V23" s="5" t="n">
-        <v>2201</v>
+        <v>1472</v>
       </c>
       <c r="W23" s="5" t="n">
         <v>4</v>
@@ -2182,10 +2212,10 @@
         <v>12</v>
       </c>
       <c r="U24" s="5" t="n">
-        <v>719</v>
+        <v>0</v>
       </c>
       <c r="V24" s="5" t="n">
-        <v>2132</v>
+        <v>1425</v>
       </c>
       <c r="W24" s="5" t="n">
         <v>0</v>
@@ -2262,7 +2292,7 @@
         <v>495</v>
       </c>
       <c r="V25" s="5" t="n">
-        <v>1471</v>
+        <v>1478</v>
       </c>
       <c r="W25" s="5" t="n">
         <v>4</v>
@@ -2336,10 +2366,10 @@
         <v>7</v>
       </c>
       <c r="U26" s="5" t="n">
-        <v>638</v>
+        <v>0</v>
       </c>
       <c r="V26" s="5" t="n">
-        <v>1899</v>
+        <v>1268</v>
       </c>
       <c r="W26" s="5" t="n">
         <v>4</v>
@@ -2413,10 +2443,10 @@
         <v>4</v>
       </c>
       <c r="U27" s="5" t="n">
-        <v>632</v>
+        <v>0</v>
       </c>
       <c r="V27" s="5" t="n">
-        <v>1885</v>
+        <v>1257</v>
       </c>
       <c r="W27" s="5" t="n">
         <v>0</v>
@@ -2485,7 +2515,7 @@
         <v>17</v>
       </c>
       <c r="S28" s="5" t="n">
-        <v>18</v>
+        <v>135</v>
       </c>
       <c r="T28" s="5" t="n">
         <v>19</v>
@@ -2494,7 +2524,7 @@
         <v>20</v>
       </c>
       <c r="V28" s="5" t="n">
-        <v>21</v>
+        <v>174</v>
       </c>
       <c r="W28" s="5" t="n">
         <v>0</v>
@@ -2568,10 +2598,10 @@
         <v>6</v>
       </c>
       <c r="U29" s="5" t="n">
-        <v>875</v>
+        <v>0</v>
       </c>
       <c r="V29" s="5" t="n">
-        <v>2606</v>
+        <v>1737</v>
       </c>
       <c r="W29" s="5" t="n">
         <v>0</v>
@@ -2645,10 +2675,10 @@
         <v>15</v>
       </c>
       <c r="U30" s="5" t="n">
-        <v>609</v>
+        <v>0</v>
       </c>
       <c r="V30" s="5" t="n">
-        <v>1797</v>
+        <v>1203</v>
       </c>
       <c r="W30" s="5" t="n">
         <v>0</v>
@@ -2722,10 +2752,10 @@
         <v>28</v>
       </c>
       <c r="U31" s="5" t="n">
-        <v>703</v>
+        <v>0</v>
       </c>
       <c r="V31" s="5" t="n">
-        <v>2052</v>
+        <v>1377</v>
       </c>
       <c r="W31" s="5" t="n">
         <v>0</v>
@@ -2799,10 +2829,10 @@
         <v>0</v>
       </c>
       <c r="U32" s="5" t="n">
-        <v>626</v>
+        <v>0</v>
       </c>
       <c r="V32" s="5" t="n">
-        <v>1904</v>
+        <v>1278</v>
       </c>
       <c r="W32" s="5" t="n">
         <v>0</v>
@@ -2876,10 +2906,10 @@
         <v>10</v>
       </c>
       <c r="U33" s="5" t="n">
-        <v>797</v>
+        <v>0</v>
       </c>
       <c r="V33" s="5" t="n">
-        <v>2371</v>
+        <v>1584</v>
       </c>
       <c r="W33" s="5" t="n">
         <v>0</v>
@@ -2953,10 +2983,10 @@
         <v>12</v>
       </c>
       <c r="U34" s="5" t="n">
-        <v>695</v>
+        <v>0</v>
       </c>
       <c r="V34" s="5" t="n">
-        <v>2061</v>
+        <v>1378</v>
       </c>
       <c r="W34" s="5" t="n">
         <v>0</v>
@@ -3030,10 +3060,10 @@
         <v>10</v>
       </c>
       <c r="U35" s="5" t="n">
-        <v>692</v>
+        <v>0</v>
       </c>
       <c r="V35" s="5" t="n">
-        <v>1684</v>
+        <v>1002</v>
       </c>
       <c r="W35" s="5" t="n">
         <v>0</v>
@@ -3110,7 +3140,7 @@
         <v>403</v>
       </c>
       <c r="V36" s="5" t="n">
-        <v>1187</v>
+        <v>1198</v>
       </c>
       <c r="W36" s="5" t="n">
         <v>0</v>
@@ -3187,7 +3217,7 @@
         <v>451</v>
       </c>
       <c r="V37" s="5" t="n">
-        <v>1343</v>
+        <v>1348</v>
       </c>
       <c r="W37" s="5" t="n">
         <v>0</v>
@@ -3261,10 +3291,10 @@
         <v>19</v>
       </c>
       <c r="U38" s="5" t="n">
-        <v>724</v>
+        <v>0</v>
       </c>
       <c r="V38" s="5" t="n">
-        <v>2134</v>
+        <v>1429</v>
       </c>
       <c r="W38" s="5" t="n">
         <v>0</v>
@@ -3341,7 +3371,7 @@
         <v>480</v>
       </c>
       <c r="V39" s="5" t="n">
-        <v>1424</v>
+        <v>1432</v>
       </c>
       <c r="W39" s="5" t="n">
         <v>0</v>
@@ -3415,10 +3445,10 @@
         <v>3</v>
       </c>
       <c r="U40" s="5" t="n">
-        <v>508</v>
+        <v>0</v>
       </c>
       <c r="V40" s="5" t="n">
-        <v>1521</v>
+        <v>1016</v>
       </c>
       <c r="W40" s="5" t="n">
         <v>0</v>
@@ -3572,7 +3602,7 @@
         <v>356</v>
       </c>
       <c r="V42" s="5" t="n">
-        <v>1058</v>
+        <v>1062</v>
       </c>
       <c r="W42" s="5" t="n">
         <v>0</v>
@@ -3646,10 +3676,10 @@
         <v>9</v>
       </c>
       <c r="U43" s="5" t="n">
-        <v>767</v>
+        <v>0</v>
       </c>
       <c r="V43" s="5" t="n">
-        <v>2586</v>
+        <v>1828</v>
       </c>
       <c r="W43" s="5" t="n">
         <v>0</v>
@@ -3723,10 +3753,10 @@
         <v>4</v>
       </c>
       <c r="U44" s="5" t="n">
-        <v>626</v>
+        <v>0</v>
       </c>
       <c r="V44" s="5" t="n">
-        <v>1770</v>
+        <v>1148</v>
       </c>
       <c r="W44" s="5" t="n">
         <v>0</v>
@@ -3803,7 +3833,7 @@
         <v>476</v>
       </c>
       <c r="V45" s="5" t="n">
-        <v>1433</v>
+        <v>1437</v>
       </c>
       <c r="W45" s="5" t="n">
         <v>0</v>
@@ -3877,10 +3907,10 @@
         <v>0</v>
       </c>
       <c r="U46" s="5" t="n">
-        <v>764</v>
+        <v>0</v>
       </c>
       <c r="V46" s="5" t="n">
-        <v>2288</v>
+        <v>1524</v>
       </c>
       <c r="W46" s="5" t="n">
         <v>0</v>
@@ -3954,10 +3984,10 @@
         <v>10</v>
       </c>
       <c r="U47" s="5" t="n">
-        <v>794</v>
+        <v>0</v>
       </c>
       <c r="V47" s="5" t="n">
-        <v>2361</v>
+        <v>1577</v>
       </c>
       <c r="W47" s="5" t="n">
         <v>0</v>
@@ -4031,10 +4061,10 @@
         <v>8</v>
       </c>
       <c r="U48" s="5" t="n">
-        <v>740</v>
+        <v>0</v>
       </c>
       <c r="V48" s="5" t="n">
-        <v>2198</v>
+        <v>1466</v>
       </c>
       <c r="W48" s="5" t="n">
         <v>0</v>
@@ -4111,7 +4141,7 @@
         <v>224</v>
       </c>
       <c r="V49" s="5" t="n">
-        <v>659</v>
+        <v>663</v>
       </c>
       <c r="W49" s="5" t="n">
         <v>0</v>
@@ -4185,10 +4215,10 @@
         <v>5</v>
       </c>
       <c r="U50" s="5" t="n">
-        <v>535</v>
+        <v>0</v>
       </c>
       <c r="V50" s="5" t="n">
-        <v>1608</v>
+        <v>1078</v>
       </c>
       <c r="W50" s="5" t="n">
         <v>0</v>
@@ -4262,10 +4292,10 @@
         <v>44</v>
       </c>
       <c r="U51" s="5" t="n">
-        <v>710</v>
+        <v>0</v>
       </c>
       <c r="V51" s="5" t="n">
-        <v>2141</v>
+        <v>1475</v>
       </c>
       <c r="W51" s="5" t="n">
         <v>0</v>
@@ -4339,10 +4369,10 @@
         <v>8</v>
       </c>
       <c r="U52" s="5" t="n">
-        <v>617</v>
+        <v>0</v>
       </c>
       <c r="V52" s="5" t="n">
-        <v>1851</v>
+        <v>1242</v>
       </c>
       <c r="W52" s="5" t="n">
         <v>0</v>
@@ -4416,10 +4446,10 @@
         <v>13</v>
       </c>
       <c r="U53" s="5" t="n">
-        <v>815</v>
+        <v>0</v>
       </c>
       <c r="V53" s="5" t="n">
-        <v>2438</v>
+        <v>1636</v>
       </c>
       <c r="W53" s="5" t="n">
         <v>0</v>
@@ -4493,10 +4523,10 @@
         <v>13</v>
       </c>
       <c r="U54" s="5" t="n">
-        <v>963</v>
+        <v>0</v>
       </c>
       <c r="V54" s="5" t="n">
-        <v>2847</v>
+        <v>1897</v>
       </c>
       <c r="W54" s="5" t="n">
         <v>0</v>
@@ -4570,10 +4600,10 @@
         <v>10</v>
       </c>
       <c r="U55" s="5" t="n">
-        <v>581</v>
+        <v>0</v>
       </c>
       <c r="V55" s="5" t="n">
-        <v>1839</v>
+        <v>1268</v>
       </c>
       <c r="W55" s="5" t="n">
         <v>0</v>
@@ -4647,10 +4677,10 @@
         <v>9</v>
       </c>
       <c r="U56" s="5" t="n">
-        <v>518</v>
+        <v>0</v>
       </c>
       <c r="V56" s="5" t="n">
-        <v>1552</v>
+        <v>1043</v>
       </c>
       <c r="W56" s="5" t="n">
         <v>0</v>
@@ -4727,7 +4757,7 @@
         <v>467</v>
       </c>
       <c r="V57" s="5" t="n">
-        <v>1432</v>
+        <v>1436</v>
       </c>
       <c r="W57" s="5" t="n">
         <v>0</v>
@@ -4804,7 +4834,7 @@
         <v>342</v>
       </c>
       <c r="V58" s="5" t="n">
-        <v>1033</v>
+        <v>1447</v>
       </c>
       <c r="W58" s="5" t="n">
         <v>0</v>
@@ -4872,7 +4902,7 @@
         <v>17</v>
       </c>
       <c r="S59" s="5" t="n">
-        <v>18</v>
+        <v>134</v>
       </c>
       <c r="T59" s="5" t="n">
         <v>19</v>
@@ -4881,7 +4911,7 @@
         <v>20</v>
       </c>
       <c r="V59" s="5" t="n">
-        <v>21</v>
+        <v>173</v>
       </c>
       <c r="W59" s="5" t="n">
         <v>0</v>
@@ -4955,10 +4985,10 @@
         <v>0</v>
       </c>
       <c r="U60" s="5" t="n">
-        <v>557</v>
+        <v>0</v>
       </c>
       <c r="V60" s="5" t="n">
-        <v>1641</v>
+        <v>1084</v>
       </c>
       <c r="W60" s="5" t="n">
         <v>0</v>
@@ -5032,10 +5062,10 @@
         <v>16</v>
       </c>
       <c r="U61" s="5" t="n">
-        <v>1022</v>
+        <v>0</v>
       </c>
       <c r="V61" s="5" t="n">
-        <v>3374</v>
+        <v>2368</v>
       </c>
       <c r="W61" s="5" t="n">
         <v>0</v>
@@ -5112,7 +5142,7 @@
         <v>468</v>
       </c>
       <c r="V62" s="5" t="n">
-        <v>1320</v>
+        <v>1328</v>
       </c>
       <c r="W62" s="5" t="n">
         <v>3</v>
@@ -5343,7 +5373,7 @@
         <v>321</v>
       </c>
       <c r="V65" s="5" t="n">
-        <v>878</v>
+        <v>880</v>
       </c>
       <c r="W65" s="5" t="n">
         <v>0</v>
@@ -5417,10 +5447,10 @@
         <v>8</v>
       </c>
       <c r="U66" s="5" t="n">
-        <v>788</v>
+        <v>0</v>
       </c>
       <c r="V66" s="5" t="n">
-        <v>2373</v>
+        <v>1593</v>
       </c>
       <c r="W66" s="5" t="n">
         <v>4</v>
@@ -5494,10 +5524,10 @@
         <v>13</v>
       </c>
       <c r="U67" s="5" t="n">
-        <v>941</v>
+        <v>0</v>
       </c>
       <c r="V67" s="5" t="n">
-        <v>3096</v>
+        <v>2168</v>
       </c>
       <c r="W67" s="5" t="n">
         <v>0</v>
@@ -5571,10 +5601,10 @@
         <v>17</v>
       </c>
       <c r="U68" s="5" t="n">
-        <v>563</v>
+        <v>0</v>
       </c>
       <c r="V68" s="5" t="n">
-        <v>2019</v>
+        <v>1473</v>
       </c>
       <c r="W68" s="5" t="n">
         <v>4</v>
@@ -5651,7 +5681,7 @@
         <v>396</v>
       </c>
       <c r="V69" s="5" t="n">
-        <v>1184</v>
+        <v>1186</v>
       </c>
       <c r="W69" s="5" t="n">
         <v>0</v>
@@ -5728,7 +5758,7 @@
         <v>193</v>
       </c>
       <c r="V70" s="5" t="n">
-        <v>570</v>
+        <v>576</v>
       </c>
       <c r="W70" s="5" t="n">
         <v>0</v>
@@ -5802,10 +5832,10 @@
         <v>7</v>
       </c>
       <c r="U71" s="5" t="n">
-        <v>765</v>
+        <v>0</v>
       </c>
       <c r="V71" s="5" t="n">
-        <v>2177</v>
+        <v>1419</v>
       </c>
       <c r="W71" s="5" t="n">
         <v>0</v>
@@ -5882,7 +5912,7 @@
         <v>241</v>
       </c>
       <c r="V72" s="5" t="n">
-        <v>751</v>
+        <v>754</v>
       </c>
       <c r="W72" s="5" t="n">
         <v>0</v>
@@ -5956,10 +5986,10 @@
         <v>20</v>
       </c>
       <c r="U73" s="5" t="n">
-        <v>873</v>
+        <v>0</v>
       </c>
       <c r="V73" s="5" t="n">
-        <v>90</v>
+        <v>1932</v>
       </c>
       <c r="W73" s="5" t="n">
         <v>0</v>
@@ -6033,10 +6063,10 @@
         <v>2</v>
       </c>
       <c r="U74" s="5" t="n">
-        <v>505</v>
+        <v>0</v>
       </c>
       <c r="V74" s="5" t="n">
-        <v>1459</v>
+        <v>956</v>
       </c>
       <c r="W74" s="5" t="n">
         <v>0</v>
@@ -6111,10 +6141,10 @@
         <v>6</v>
       </c>
       <c r="U75" s="5" t="n">
-        <v>698</v>
+        <v>0</v>
       </c>
       <c r="V75" s="5" t="n">
-        <v>2115</v>
+        <v>1423</v>
       </c>
       <c r="W75" s="5" t="n">
         <v>0</v>
@@ -6188,10 +6218,10 @@
         <v>14</v>
       </c>
       <c r="U76" s="5" t="n">
-        <v>838</v>
+        <v>0</v>
       </c>
       <c r="V76" s="5" t="n">
-        <v>2176</v>
+        <v>1352</v>
       </c>
       <c r="W76" s="5" t="n">
         <v>0</v>
@@ -6268,7 +6298,7 @@
         <v>13</v>
       </c>
       <c r="V77" s="5" t="n">
-        <v>1000</v>
+        <v>1006</v>
       </c>
       <c r="W77" s="5" t="n">
         <v>0</v>
@@ -6345,7 +6375,7 @@
         <v>447</v>
       </c>
       <c r="V78" s="5" t="n">
-        <v>1271</v>
+        <v>1279</v>
       </c>
       <c r="W78" s="5" t="n">
         <v>0</v>
@@ -6496,10 +6526,10 @@
         <v>14</v>
       </c>
       <c r="U80" s="5" t="n">
-        <v>832</v>
+        <v>0</v>
       </c>
       <c r="V80" s="5" t="n">
-        <v>2480</v>
+        <v>1662</v>
       </c>
       <c r="W80" s="5" t="n">
         <v>0</v>
@@ -6573,10 +6603,10 @@
         <v>416</v>
       </c>
       <c r="U81" s="5" t="n">
-        <v>894</v>
+        <v>0</v>
       </c>
       <c r="V81" s="5" t="n">
-        <v>3053</v>
+        <v>2575</v>
       </c>
       <c r="W81" s="5" t="n">
         <v>0</v>
@@ -6650,10 +6680,10 @@
         <v>16</v>
       </c>
       <c r="U82" s="5" t="n">
-        <v>973</v>
+        <v>0</v>
       </c>
       <c r="V82" s="5" t="n">
-        <v>2738</v>
+        <v>1781</v>
       </c>
       <c r="W82" s="5" t="n">
         <v>0</v>
@@ -6727,10 +6757,10 @@
         <v>412</v>
       </c>
       <c r="U83" s="5" t="n">
-        <v>653</v>
+        <v>0</v>
       </c>
       <c r="V83" s="5" t="n">
-        <v>1927</v>
+        <v>1686</v>
       </c>
       <c r="W83" s="5" t="n">
         <v>0</v>
@@ -6804,10 +6834,10 @@
         <v>4</v>
       </c>
       <c r="U84" s="5" t="n">
-        <v>669</v>
+        <v>0</v>
       </c>
       <c r="V84" s="5" t="n">
-        <v>1786</v>
+        <v>1121</v>
       </c>
       <c r="W84" s="5" t="n">
         <v>0</v>
@@ -6881,10 +6911,10 @@
         <v>13</v>
       </c>
       <c r="U85" s="5" t="n">
-        <v>715</v>
+        <v>0</v>
       </c>
       <c r="V85" s="5" t="n">
-        <v>1843</v>
+        <v>1141</v>
       </c>
       <c r="W85" s="5" t="n">
         <v>0</v>
@@ -6913,7 +6943,7 @@
         <v>0</v>
       </c>
       <c r="F86" s="5" t="n">
-        <v>4169</v>
+        <v>0</v>
       </c>
       <c r="G86" s="5" t="n">
         <v>0</v>
@@ -6952,7 +6982,7 @@
         <v>385</v>
       </c>
       <c r="S86" s="5" t="n">
-        <v>5083</v>
+        <v>914</v>
       </c>
       <c r="T86" s="5" t="n">
         <v>28</v>
@@ -6961,7 +6991,7 @@
         <v>413</v>
       </c>
       <c r="V86" s="5" t="n">
-        <v>5496</v>
+        <v>1355</v>
       </c>
       <c r="W86" s="5" t="n">
         <v>0</v>
@@ -7038,7 +7068,7 @@
         <v>355</v>
       </c>
       <c r="V87" s="5" t="n">
-        <v>1015</v>
+        <v>1029</v>
       </c>
       <c r="W87" s="5" t="n">
         <v>0</v>
@@ -7112,10 +7142,10 @@
         <v>41</v>
       </c>
       <c r="U88" s="5" t="n">
-        <v>604</v>
+        <v>0</v>
       </c>
       <c r="V88" s="5" t="n">
-        <v>1485</v>
+        <v>922</v>
       </c>
       <c r="W88" s="5" t="n">
         <v>0</v>
@@ -7189,10 +7219,10 @@
         <v>0</v>
       </c>
       <c r="U89" s="5" t="n">
-        <v>538</v>
+        <v>0</v>
       </c>
       <c r="V89" s="5" t="n">
-        <v>2023</v>
+        <v>1485</v>
       </c>
       <c r="W89" s="5" t="n">
         <v>0</v>
@@ -7266,10 +7296,10 @@
         <v>0</v>
       </c>
       <c r="U90" s="5" t="n">
-        <v>597</v>
+        <v>0</v>
       </c>
       <c r="V90" s="5" t="n">
-        <v>1351</v>
+        <v>754</v>
       </c>
       <c r="W90" s="5" t="n">
         <v>0</v>
@@ -7338,7 +7368,7 @@
         <v>7</v>
       </c>
       <c r="S91" s="5" t="n">
-        <v>18</v>
+        <v>142</v>
       </c>
       <c r="T91" s="5" t="n">
         <v>19</v>
@@ -7347,7 +7377,7 @@
         <v>20</v>
       </c>
       <c r="V91" s="5" t="n">
-        <v>21</v>
+        <v>181</v>
       </c>
       <c r="W91" s="5" t="n">
         <v>0</v>
@@ -7424,7 +7454,7 @@
         <v>368</v>
       </c>
       <c r="V92" s="5" t="n">
-        <v>1084</v>
+        <v>1094</v>
       </c>
       <c r="W92" s="5" t="n">
         <v>0</v>
@@ -7501,7 +7531,7 @@
         <v>437</v>
       </c>
       <c r="V93" s="5" t="n">
-        <v>1305</v>
+        <v>1308</v>
       </c>
       <c r="W93" s="5" t="n">
         <v>0</v>
@@ -7575,10 +7605,10 @@
         <v>23</v>
       </c>
       <c r="U94" s="5" t="n">
-        <v>625</v>
+        <v>0</v>
       </c>
       <c r="V94" s="5" t="n">
-        <v>1825</v>
+        <v>1223</v>
       </c>
       <c r="W94" s="5" t="n">
         <v>0</v>
@@ -7652,10 +7682,10 @@
         <v>0</v>
       </c>
       <c r="U95" s="5" t="n">
-        <v>610</v>
+        <v>0</v>
       </c>
       <c r="V95" s="5" t="n">
-        <v>1843</v>
+        <v>1233</v>
       </c>
       <c r="W95" s="5" t="n">
         <v>0</v>
@@ -7729,10 +7759,10 @@
         <v>0</v>
       </c>
       <c r="U96" s="5" t="n">
-        <v>514</v>
+        <v>0</v>
       </c>
       <c r="V96" s="5" t="n">
-        <v>1522</v>
+        <v>1008</v>
       </c>
       <c r="W96" s="5" t="n">
         <v>0</v>
@@ -7806,10 +7836,10 @@
         <v>6</v>
       </c>
       <c r="U97" s="5" t="n">
-        <v>570</v>
+        <v>0</v>
       </c>
       <c r="V97" s="5" t="n">
-        <v>1996</v>
+        <v>1432</v>
       </c>
       <c r="W97" s="5" t="n">
         <v>0</v>
@@ -7883,10 +7913,10 @@
         <v>17</v>
       </c>
       <c r="U98" s="5" t="n">
-        <v>714</v>
+        <v>0</v>
       </c>
       <c r="V98" s="5" t="n">
-        <v>2108</v>
+        <v>1411</v>
       </c>
       <c r="W98" s="5" t="n">
         <v>0</v>
@@ -7960,10 +7990,10 @@
         <v>8</v>
       </c>
       <c r="U99" s="5" t="n">
-        <v>674</v>
+        <v>0</v>
       </c>
       <c r="V99" s="5" t="n">
-        <v>2009</v>
+        <v>1343</v>
       </c>
       <c r="W99" s="5" t="n">
         <v>0</v>
@@ -8037,10 +8067,10 @@
         <v>18</v>
       </c>
       <c r="U100" s="5" t="n">
-        <v>830</v>
+        <v>0</v>
       </c>
       <c r="V100" s="5" t="n">
-        <v>2454</v>
+        <v>1642</v>
       </c>
       <c r="W100" s="5" t="n">
         <v>0</v>
@@ -8117,7 +8147,7 @@
         <v>456</v>
       </c>
       <c r="V101" s="5" t="n">
-        <v>1377</v>
+        <v>1392</v>
       </c>
       <c r="W101" s="5" t="n">
         <v>0</v>
@@ -8268,10 +8298,10 @@
         <v>1</v>
       </c>
       <c r="U103" s="5" t="n">
-        <v>610</v>
+        <v>0</v>
       </c>
       <c r="V103" s="5" t="n">
-        <v>1808</v>
+        <v>1199</v>
       </c>
       <c r="W103" s="5" t="n">
         <v>0</v>
@@ -8345,10 +8375,10 @@
         <v>18</v>
       </c>
       <c r="U104" s="5" t="n">
-        <v>802</v>
+        <v>0</v>
       </c>
       <c r="V104" s="5" t="n">
-        <v>2670</v>
+        <v>1886</v>
       </c>
       <c r="W104" s="5" t="n">
         <v>0</v>
@@ -8422,10 +8452,10 @@
         <v>8</v>
       </c>
       <c r="U105" s="5" t="n">
-        <v>670</v>
+        <v>0</v>
       </c>
       <c r="V105" s="5" t="n">
-        <v>1984</v>
+        <v>1322</v>
       </c>
       <c r="W105" s="5" t="n">
         <v>0</v>
@@ -8499,10 +8529,10 @@
         <v>6</v>
       </c>
       <c r="U106" s="5" t="n">
-        <v>598</v>
+        <v>0</v>
       </c>
       <c r="V106" s="5" t="n">
-        <v>1785</v>
+        <v>1193</v>
       </c>
       <c r="W106" s="5" t="n">
         <v>0</v>
@@ -8576,10 +8606,10 @@
         <v>10</v>
       </c>
       <c r="U107" s="5" t="n">
-        <v>901</v>
+        <v>0</v>
       </c>
       <c r="V107" s="5" t="n">
-        <v>2683</v>
+        <v>1792</v>
       </c>
       <c r="W107" s="5" t="n">
         <v>0</v>
@@ -8653,10 +8683,10 @@
         <v>415</v>
       </c>
       <c r="U108" s="5" t="n">
-        <v>785</v>
+        <v>0</v>
       </c>
       <c r="V108" s="5" t="n">
-        <v>2328</v>
+        <v>1958</v>
       </c>
       <c r="W108" s="5" t="n">
         <v>0</v>
@@ -8730,10 +8760,10 @@
         <v>9</v>
       </c>
       <c r="U109" s="5" t="n">
-        <v>880</v>
+        <v>0</v>
       </c>
       <c r="V109" s="5" t="n">
-        <v>2628</v>
+        <v>1757</v>
       </c>
       <c r="W109" s="5" t="n">
         <v>0</v>
@@ -8807,10 +8837,10 @@
         <v>0</v>
       </c>
       <c r="U110" s="5" t="n">
-        <v>506</v>
+        <v>0</v>
       </c>
       <c r="V110" s="5" t="n">
-        <v>1508</v>
+        <v>1002</v>
       </c>
       <c r="W110" s="5" t="n">
         <v>0</v>
@@ -8884,10 +8914,10 @@
         <v>6</v>
       </c>
       <c r="U111" s="5" t="n">
-        <v>599</v>
+        <v>0</v>
       </c>
       <c r="V111" s="5" t="n">
-        <v>1791</v>
+        <v>1198</v>
       </c>
       <c r="W111" s="5" t="n">
         <v>0</v>
@@ -8964,7 +8994,7 @@
         <v>499</v>
       </c>
       <c r="V112" s="5" t="n">
-        <v>1494</v>
+        <v>1497</v>
       </c>
       <c r="W112" s="5" t="n">
         <v>0</v>
@@ -9038,10 +9068,10 @@
         <v>0</v>
       </c>
       <c r="U113" s="5" t="n">
-        <v>505</v>
+        <v>0</v>
       </c>
       <c r="V113" s="5" t="n">
-        <v>1540</v>
+        <v>1035</v>
       </c>
       <c r="W113" s="5" t="n">
         <v>0</v>
@@ -9115,10 +9145,10 @@
         <v>417</v>
       </c>
       <c r="U114" s="5" t="n">
-        <v>704</v>
+        <v>0</v>
       </c>
       <c r="V114" s="5" t="n">
-        <v>2103</v>
+        <v>1816</v>
       </c>
       <c r="W114" s="5" t="n">
         <v>0</v>
@@ -9349,7 +9379,7 @@
         <v>22</v>
       </c>
       <c r="V117" s="5" t="n">
-        <v>1052</v>
+        <v>1055</v>
       </c>
       <c r="W117" s="5" t="n">
         <v>0</v>
@@ -9426,7 +9456,7 @@
         <v>488</v>
       </c>
       <c r="V118" s="5" t="n">
-        <v>1293</v>
+        <v>1294</v>
       </c>
       <c r="W118" s="5" t="n">
         <v>0</v>
@@ -9503,7 +9533,7 @@
         <v>418</v>
       </c>
       <c r="V119" s="5" t="n">
-        <v>1148</v>
+        <v>1160</v>
       </c>
       <c r="W119" s="5" t="n">
         <v>0</v>
@@ -9577,10 +9607,10 @@
         <v>139</v>
       </c>
       <c r="U120" s="5" t="n">
-        <v>531</v>
+        <v>0</v>
       </c>
       <c r="V120" s="5" t="n">
-        <v>1577</v>
+        <v>1185</v>
       </c>
       <c r="W120" s="5" t="n">
         <v>0</v>
@@ -9654,10 +9684,10 @@
         <v>8</v>
       </c>
       <c r="U121" s="5" t="n">
-        <v>597</v>
+        <v>0</v>
       </c>
       <c r="V121" s="5" t="n">
-        <v>1778</v>
+        <v>1189</v>
       </c>
       <c r="W121" s="5" t="n">
         <v>0</v>
@@ -9811,7 +9841,7 @@
         <v>475</v>
       </c>
       <c r="V123" s="5" t="n">
-        <v>1531</v>
+        <v>1539</v>
       </c>
       <c r="W123" s="5" t="n">
         <v>0</v>
@@ -9879,7 +9909,7 @@
         <v>17</v>
       </c>
       <c r="S124" s="5" t="n">
-        <v>8</v>
+        <v>136</v>
       </c>
       <c r="T124" s="5" t="n">
         <v>19</v>
@@ -9888,7 +9918,7 @@
         <v>20</v>
       </c>
       <c r="V124" s="5" t="n">
-        <v>4</v>
+        <v>175</v>
       </c>
       <c r="W124" s="5" t="n">
         <v>0</v>
@@ -9965,7 +9995,7 @@
         <v>456</v>
       </c>
       <c r="V125" s="5" t="n">
-        <v>1404</v>
+        <v>1409</v>
       </c>
       <c r="W125" s="5" t="n">
         <v>0</v>
@@ -10120,7 +10150,7 @@
         <v>435</v>
       </c>
       <c r="V127" s="5" t="n">
-        <v>1340</v>
+        <v>1344</v>
       </c>
       <c r="W127" s="5" t="n">
         <v>0</v>
@@ -10194,10 +10224,10 @@
         <v>14</v>
       </c>
       <c r="U128" s="5" t="n">
-        <v>678</v>
+        <v>0</v>
       </c>
       <c r="V128" s="5" t="n">
-        <v>2008</v>
+        <v>1344</v>
       </c>
       <c r="W128" s="5" t="n">
         <v>0</v>
@@ -10271,10 +10301,10 @@
         <v>7</v>
       </c>
       <c r="U129" s="5" t="n">
-        <v>561</v>
+        <v>0</v>
       </c>
       <c r="V129" s="5" t="n">
-        <v>1669</v>
+        <v>1115</v>
       </c>
       <c r="W129" s="5" t="n">
         <v>0</v>
@@ -10342,16 +10372,16 @@
         <v>524</v>
       </c>
       <c r="S130" s="5" t="n">
-        <v>10</v>
+        <v>1035</v>
       </c>
       <c r="T130" s="5" t="n">
         <v>13</v>
       </c>
       <c r="U130" s="5" t="n">
-        <v>537</v>
+        <v>0</v>
       </c>
       <c r="V130" s="5" t="n">
-        <v>547</v>
+        <v>1048</v>
       </c>
       <c r="W130" s="5" t="n">
         <v>0</v>
@@ -10419,16 +10449,16 @@
         <v>529</v>
       </c>
       <c r="S131" s="5" t="n">
-        <v>110</v>
+        <v>972</v>
       </c>
       <c r="T131" s="5" t="n">
         <v>5</v>
       </c>
       <c r="U131" s="5" t="n">
-        <v>534</v>
+        <v>0</v>
       </c>
       <c r="V131" s="5" t="n">
-        <v>644</v>
+        <v>977</v>
       </c>
       <c r="W131" s="5" t="n">
         <v>0</v>
@@ -10505,7 +10535,7 @@
         <v>306</v>
       </c>
       <c r="V132" s="5" t="n">
-        <v>883</v>
+        <v>900</v>
       </c>
       <c r="W132" s="5" t="n">
         <v>0</v>
@@ -10579,10 +10609,10 @@
         <v>8</v>
       </c>
       <c r="U133" s="5" t="n">
-        <v>555</v>
+        <v>0</v>
       </c>
       <c r="V133" s="5" t="n">
-        <v>1647</v>
+        <v>1100</v>
       </c>
       <c r="W133" s="5" t="n">
         <v>0</v>
@@ -10659,7 +10689,7 @@
         <v>229</v>
       </c>
       <c r="V134" s="5" t="n">
-        <v>690</v>
+        <v>693</v>
       </c>
       <c r="W134" s="5" t="n">
         <v>0</v>
@@ -10733,10 +10763,10 @@
         <v>10</v>
       </c>
       <c r="U135" s="5" t="n">
-        <v>686</v>
+        <v>0</v>
       </c>
       <c r="V135" s="5" t="n">
-        <v>2038</v>
+        <v>1362</v>
       </c>
       <c r="W135" s="5" t="n">
         <v>0</v>
@@ -10810,10 +10840,10 @@
         <v>0</v>
       </c>
       <c r="U136" s="5" t="n">
-        <v>592</v>
+        <v>0</v>
       </c>
       <c r="V136" s="5" t="n">
-        <v>1802</v>
+        <v>1210</v>
       </c>
       <c r="W136" s="5" t="n">
         <v>0</v>
@@ -10887,10 +10917,10 @@
         <v>14</v>
       </c>
       <c r="U137" s="5" t="n">
-        <v>941</v>
+        <v>0</v>
       </c>
       <c r="V137" s="5" t="n">
-        <v>2795</v>
+        <v>1868</v>
       </c>
       <c r="W137" s="5" t="n">
         <v>0</v>
@@ -10964,10 +10994,10 @@
         <v>0</v>
       </c>
       <c r="U138" s="5" t="n">
-        <v>592</v>
+        <v>0</v>
       </c>
       <c r="V138" s="5" t="n">
-        <v>1735</v>
+        <v>1143</v>
       </c>
       <c r="W138" s="5" t="n">
         <v>0</v>
@@ -10987,7 +11017,7 @@
         </is>
       </c>
       <c r="C139" s="5" t="n">
-        <v>2325</v>
+        <v>0</v>
       </c>
       <c r="D139" s="5" t="n">
         <v>10</v>
@@ -11035,16 +11065,16 @@
         <v>541</v>
       </c>
       <c r="S139" s="5" t="n">
-        <v>3172</v>
+        <v>847</v>
       </c>
       <c r="T139" s="5" t="n">
         <v>10</v>
       </c>
       <c r="U139" s="5" t="n">
-        <v>551</v>
+        <v>0</v>
       </c>
       <c r="V139" s="5" t="n">
-        <v>3723</v>
+        <v>857</v>
       </c>
       <c r="W139" s="5" t="n">
         <v>0</v>
@@ -11118,10 +11148,10 @@
         <v>13</v>
       </c>
       <c r="U140" s="5" t="n">
-        <v>859</v>
+        <v>0</v>
       </c>
       <c r="V140" s="5" t="n">
-        <v>2554</v>
+        <v>1708</v>
       </c>
       <c r="W140" s="5" t="n">
         <v>0</v>
@@ -11195,10 +11225,10 @@
         <v>11</v>
       </c>
       <c r="U141" s="5" t="n">
-        <v>637</v>
+        <v>0</v>
       </c>
       <c r="V141" s="5" t="n">
-        <v>1889</v>
+        <v>1263</v>
       </c>
       <c r="W141" s="5" t="n">
         <v>0</v>
@@ -11272,10 +11302,10 @@
         <v>8</v>
       </c>
       <c r="U142" s="5" t="n">
-        <v>690</v>
+        <v>0</v>
       </c>
       <c r="V142" s="5" t="n">
-        <v>2526</v>
+        <v>1844</v>
       </c>
       <c r="W142" s="5" t="n">
         <v>0</v>
@@ -11352,7 +11382,7 @@
         <v>358</v>
       </c>
       <c r="V143" s="5" t="n">
-        <v>1065</v>
+        <v>1071</v>
       </c>
       <c r="W143" s="5" t="n">
         <v>0</v>
@@ -11426,10 +11456,10 @@
         <v>17</v>
       </c>
       <c r="U144" s="5" t="n">
-        <v>744</v>
+        <v>0</v>
       </c>
       <c r="V144" s="5" t="n">
-        <v>2210</v>
+        <v>1483</v>
       </c>
       <c r="W144" s="5" t="n">
         <v>0</v>
@@ -11503,10 +11533,10 @@
         <v>14</v>
       </c>
       <c r="U145" s="5" t="n">
-        <v>626</v>
+        <v>0</v>
       </c>
       <c r="V145" s="5" t="n">
-        <v>1869</v>
+        <v>1257</v>
       </c>
       <c r="W145" s="5" t="n">
         <v>0</v>
@@ -11580,10 +11610,10 @@
         <v>16</v>
       </c>
       <c r="U146" s="5" t="n">
-        <v>916</v>
+        <v>0</v>
       </c>
       <c r="V146" s="5" t="n">
-        <v>2715</v>
+        <v>1815</v>
       </c>
       <c r="W146" s="5" t="n">
         <v>0</v>
@@ -11660,7 +11690,7 @@
         <v>352</v>
       </c>
       <c r="V147" s="5" t="n">
-        <v>1063</v>
+        <v>1069</v>
       </c>
       <c r="W147" s="5" t="n">
         <v>0</v>
@@ -11811,10 +11841,10 @@
         <v>0</v>
       </c>
       <c r="U149" s="5" t="n">
-        <v>713</v>
+        <v>0</v>
       </c>
       <c r="V149" s="5" t="n">
-        <v>2131</v>
+        <v>1418</v>
       </c>
       <c r="W149" s="5" t="n">
         <v>0</v>
@@ -12042,10 +12072,10 @@
         <v>0</v>
       </c>
       <c r="U152" s="5" t="n">
-        <v>629</v>
+        <v>0</v>
       </c>
       <c r="V152" s="5" t="n">
-        <v>1962</v>
+        <v>1333</v>
       </c>
       <c r="W152" s="5" t="n">
         <v>0</v>
@@ -12196,10 +12226,10 @@
         <v>0</v>
       </c>
       <c r="U154" s="5" t="n">
-        <v>588</v>
+        <v>0</v>
       </c>
       <c r="V154" s="5" t="n">
-        <v>2070</v>
+        <v>1482</v>
       </c>
       <c r="W154" s="5" t="n">
         <v>0</v>
@@ -12350,10 +12380,10 @@
         <v>0</v>
       </c>
       <c r="U156" s="5" t="n">
-        <v>581</v>
+        <v>0</v>
       </c>
       <c r="V156" s="5" t="n">
-        <v>1455</v>
+        <v>874</v>
       </c>
       <c r="W156" s="5" t="n">
         <v>0</v>
@@ -12507,7 +12537,7 @@
         <v>0</v>
       </c>
       <c r="V158" s="5" t="n">
-        <v>1973</v>
+        <v>1993</v>
       </c>
       <c r="W158" s="5" t="n">
         <v>0</v>
@@ -12577,7 +12607,7 @@
         <v>17</v>
       </c>
       <c r="S159" s="5" t="n">
-        <v>18</v>
+        <v>152</v>
       </c>
       <c r="T159" s="5" t="n">
         <v>19</v>
@@ -12586,7 +12616,7 @@
         <v>20</v>
       </c>
       <c r="V159" s="5" t="n">
-        <v>21</v>
+        <v>191</v>
       </c>
       <c r="W159" s="5" t="n">
         <v>0</v>
@@ -12660,10 +12690,10 @@
         <v>14</v>
       </c>
       <c r="U160" s="5" t="n">
-        <v>779</v>
+        <v>0</v>
       </c>
       <c r="V160" s="5" t="n">
-        <v>2009</v>
+        <v>1244</v>
       </c>
       <c r="W160" s="5" t="n">
         <v>0</v>
@@ -12737,10 +12767,10 @@
         <v>3</v>
       </c>
       <c r="U161" s="5" t="n">
-        <v>533</v>
+        <v>0</v>
       </c>
       <c r="V161" s="5" t="n">
-        <v>1593</v>
+        <v>1063</v>
       </c>
       <c r="W161" s="5" t="n">
         <v>0</v>
@@ -12817,7 +12847,7 @@
         <v>496</v>
       </c>
       <c r="V162" s="5" t="n">
-        <v>1476</v>
+        <v>1482</v>
       </c>
       <c r="W162" s="5" t="n">
         <v>0</v>
@@ -12891,10 +12921,10 @@
         <v>19</v>
       </c>
       <c r="U163" s="5" t="n">
-        <v>888</v>
+        <v>0</v>
       </c>
       <c r="V163" s="5" t="n">
-        <v>2615</v>
+        <v>1746</v>
       </c>
       <c r="W163" s="5" t="n">
         <v>0</v>
@@ -12968,10 +12998,10 @@
         <v>23</v>
       </c>
       <c r="U164" s="5" t="n">
-        <v>591</v>
+        <v>0</v>
       </c>
       <c r="V164" s="5" t="n">
-        <v>1727</v>
+        <v>1159</v>
       </c>
       <c r="W164" s="5" t="n">
         <v>0</v>
@@ -13045,10 +13075,10 @@
         <v>5</v>
       </c>
       <c r="U165" s="5" t="n">
-        <v>504</v>
+        <v>0</v>
       </c>
       <c r="V165" s="5" t="n">
-        <v>1502</v>
+        <v>1003</v>
       </c>
       <c r="W165" s="5" t="n">
         <v>0</v>
@@ -13122,10 +13152,10 @@
         <v>18</v>
       </c>
       <c r="U166" s="5" t="n">
-        <v>684</v>
+        <v>0</v>
       </c>
       <c r="V166" s="5" t="n">
-        <v>2016</v>
+        <v>1350</v>
       </c>
       <c r="W166" s="5" t="n">
         <v>0</v>
@@ -13199,10 +13229,10 @@
         <v>11</v>
       </c>
       <c r="U167" s="5" t="n">
-        <v>545</v>
+        <v>0</v>
       </c>
       <c r="V167" s="5" t="n">
-        <v>1086</v>
+        <v>552</v>
       </c>
       <c r="W167" s="5" t="n">
         <v>0</v>
@@ -13276,10 +13306,10 @@
         <v>6</v>
       </c>
       <c r="U168" s="5" t="n">
-        <v>900</v>
+        <v>0</v>
       </c>
       <c r="V168" s="5" t="n">
-        <v>2688</v>
+        <v>1794</v>
       </c>
       <c r="W168" s="5" t="n">
         <v>0</v>
@@ -13353,10 +13383,10 @@
         <v>13</v>
       </c>
       <c r="U169" s="5" t="n">
-        <v>847</v>
+        <v>0</v>
       </c>
       <c r="V169" s="5" t="n">
-        <v>2515</v>
+        <v>1681</v>
       </c>
       <c r="W169" s="5" t="n">
         <v>0</v>
@@ -13430,10 +13460,10 @@
         <v>15</v>
       </c>
       <c r="U170" s="5" t="n">
-        <v>558</v>
+        <v>0</v>
       </c>
       <c r="V170" s="5" t="n">
-        <v>1644</v>
+        <v>1101</v>
       </c>
       <c r="W170" s="5" t="n">
         <v>0</v>
@@ -13507,10 +13537,10 @@
         <v>13</v>
       </c>
       <c r="U171" s="5" t="n">
-        <v>821</v>
+        <v>0</v>
       </c>
       <c r="V171" s="5" t="n">
-        <v>2437</v>
+        <v>1629</v>
       </c>
       <c r="W171" s="5" t="n">
         <v>0</v>
@@ -13584,10 +13614,10 @@
         <v>11</v>
       </c>
       <c r="U172" s="5" t="n">
-        <v>929</v>
+        <v>0</v>
       </c>
       <c r="V172" s="5" t="n">
-        <v>2765</v>
+        <v>1847</v>
       </c>
       <c r="W172" s="5" t="n">
         <v>0</v>
@@ -13664,7 +13694,7 @@
         <v>458</v>
       </c>
       <c r="V173" s="5" t="n">
-        <v>1366</v>
+        <v>1370</v>
       </c>
       <c r="W173" s="5" t="n">
         <v>0</v>
@@ -13738,10 +13768,10 @@
         <v>22</v>
       </c>
       <c r="U174" s="5" t="n">
-        <v>688</v>
+        <v>0</v>
       </c>
       <c r="V174" s="5" t="n">
-        <v>2020</v>
+        <v>1354</v>
       </c>
       <c r="W174" s="5" t="n">
         <v>0</v>
@@ -13815,10 +13845,10 @@
         <v>6</v>
       </c>
       <c r="U175" s="5" t="n">
-        <v>513</v>
+        <v>0</v>
       </c>
       <c r="V175" s="5" t="n">
-        <v>1527</v>
+        <v>1020</v>
       </c>
       <c r="W175" s="5" t="n">
         <v>0</v>
@@ -13892,10 +13922,10 @@
         <v>23</v>
       </c>
       <c r="U176" s="5" t="n">
-        <v>986</v>
+        <v>0</v>
       </c>
       <c r="V176" s="5" t="n">
-        <v>2905</v>
+        <v>1942</v>
       </c>
       <c r="W176" s="5" t="n">
         <v>0</v>
@@ -13972,7 +14002,7 @@
         <v>461</v>
       </c>
       <c r="V177" s="5" t="n">
-        <v>1365</v>
+        <v>1374</v>
       </c>
       <c r="W177" s="5" t="n">
         <v>0</v>
@@ -14046,10 +14076,10 @@
         <v>8</v>
       </c>
       <c r="U178" s="5" t="n">
-        <v>575</v>
+        <v>0</v>
       </c>
       <c r="V178" s="5" t="n">
-        <v>1409</v>
+        <v>842</v>
       </c>
       <c r="W178" s="5" t="n">
         <v>0</v>
@@ -14123,10 +14153,10 @@
         <v>6</v>
       </c>
       <c r="U179" s="5" t="n">
-        <v>539</v>
+        <v>0</v>
       </c>
       <c r="V179" s="5" t="n">
-        <v>1611</v>
+        <v>1078</v>
       </c>
       <c r="W179" s="5" t="n">
         <v>0</v>
@@ -14203,7 +14233,7 @@
         <v>381</v>
       </c>
       <c r="V180" s="5" t="n">
-        <v>1129</v>
+        <v>1139</v>
       </c>
       <c r="W180" s="5" t="n">
         <v>0</v>
@@ -14280,7 +14310,7 @@
         <v>488</v>
       </c>
       <c r="V181" s="5" t="n">
-        <v>1452</v>
+        <v>1458</v>
       </c>
       <c r="W181" s="5" t="n">
         <v>0</v>
@@ -14354,10 +14384,10 @@
         <v>14</v>
       </c>
       <c r="U182" s="5" t="n">
-        <v>643</v>
+        <v>0</v>
       </c>
       <c r="V182" s="5" t="n">
-        <v>1937</v>
+        <v>1308</v>
       </c>
       <c r="W182" s="5" t="n">
         <v>0</v>
@@ -14431,10 +14461,10 @@
         <v>24</v>
       </c>
       <c r="U183" s="5" t="n">
-        <v>680</v>
+        <v>0</v>
       </c>
       <c r="V183" s="5" t="n">
-        <v>2025</v>
+        <v>1369</v>
       </c>
       <c r="W183" s="5" t="n">
         <v>0</v>
@@ -14508,10 +14538,10 @@
         <v>20</v>
       </c>
       <c r="U184" s="5" t="n">
-        <v>680</v>
+        <v>0</v>
       </c>
       <c r="V184" s="5" t="n">
-        <v>2006</v>
+        <v>1346</v>
       </c>
       <c r="W184" s="5" t="n">
         <v>0</v>
@@ -14588,7 +14618,7 @@
         <v>201</v>
       </c>
       <c r="V185" s="5" t="n">
-        <v>549</v>
+        <v>555</v>
       </c>
       <c r="W185" s="5" t="n">
         <v>0</v>
@@ -14662,10 +14692,10 @@
         <v>25</v>
       </c>
       <c r="U186" s="5" t="n">
-        <v>610</v>
+        <v>0</v>
       </c>
       <c r="V186" s="5" t="n">
-        <v>2184</v>
+        <v>1599</v>
       </c>
       <c r="W186" s="5" t="n">
         <v>0</v>
@@ -14739,10 +14769,10 @@
         <v>27</v>
       </c>
       <c r="U187" s="5" t="n">
-        <v>641</v>
+        <v>0</v>
       </c>
       <c r="V187" s="5" t="n">
-        <v>1877</v>
+        <v>1263</v>
       </c>
       <c r="W187" s="5" t="n">
         <v>0</v>
@@ -14819,7 +14849,7 @@
         <v>274</v>
       </c>
       <c r="V188" s="5" t="n">
-        <v>820</v>
+        <v>827</v>
       </c>
       <c r="W188" s="5" t="n">
         <v>0</v>
@@ -14896,7 +14926,7 @@
         <v>381</v>
       </c>
       <c r="V189" s="5" t="n">
-        <v>1130</v>
+        <v>1146</v>
       </c>
       <c r="W189" s="5" t="n">
         <v>0</v>
@@ -14970,10 +15000,10 @@
         <v>4</v>
       </c>
       <c r="U190" s="5" t="n">
-        <v>540</v>
+        <v>0</v>
       </c>
       <c r="V190" s="5" t="n">
-        <v>1618</v>
+        <v>1082</v>
       </c>
       <c r="W190" s="5" t="n">
         <v>0</v>
@@ -15050,7 +15080,7 @@
         <v>407</v>
       </c>
       <c r="V191" s="5" t="n">
-        <v>1215</v>
+        <v>1221</v>
       </c>
       <c r="W191" s="5" t="n">
         <v>0</v>
@@ -15118,7 +15148,7 @@
         <v>17</v>
       </c>
       <c r="S192" s="5" t="n">
-        <v>18</v>
+        <v>142</v>
       </c>
       <c r="T192" s="5" t="n">
         <v>19</v>
@@ -15127,7 +15157,7 @@
         <v>20</v>
       </c>
       <c r="V192" s="5" t="n">
-        <v>21</v>
+        <v>181</v>
       </c>
       <c r="W192" s="5" t="n">
         <v>0</v>
@@ -15201,10 +15231,10 @@
         <v>15</v>
       </c>
       <c r="U193" s="5" t="n">
-        <v>849</v>
+        <v>0</v>
       </c>
       <c r="V193" s="5" t="n">
-        <v>2517</v>
+        <v>1683</v>
       </c>
       <c r="W193" s="5" t="n">
         <v>0</v>
@@ -15278,10 +15308,10 @@
         <v>22</v>
       </c>
       <c r="U194" s="5" t="n">
-        <v>930</v>
+        <v>0</v>
       </c>
       <c r="V194" s="5" t="n">
-        <v>2746</v>
+        <v>1838</v>
       </c>
       <c r="W194" s="5" t="n">
         <v>0</v>
@@ -15355,10 +15385,10 @@
         <v>24</v>
       </c>
       <c r="U195" s="5" t="n">
-        <v>562</v>
+        <v>0</v>
       </c>
       <c r="V195" s="5" t="n">
-        <v>1641</v>
+        <v>1103</v>
       </c>
       <c r="W195" s="5" t="n">
         <v>0</v>
@@ -15432,10 +15462,10 @@
         <v>16</v>
       </c>
       <c r="U196" s="5" t="n">
-        <v>530</v>
+        <v>0</v>
       </c>
       <c r="V196" s="5" t="n">
-        <v>1561</v>
+        <v>1047</v>
       </c>
       <c r="W196" s="5" t="n">
         <v>0</v>
@@ -15509,10 +15539,10 @@
         <v>14</v>
       </c>
       <c r="U197" s="5" t="n">
-        <v>890</v>
+        <v>0</v>
       </c>
       <c r="V197" s="5" t="n">
-        <v>2642</v>
+        <v>1766</v>
       </c>
       <c r="W197" s="5" t="n">
         <v>0</v>
@@ -15589,7 +15619,7 @@
         <v>492</v>
       </c>
       <c r="V198" s="5" t="n">
-        <v>1434</v>
+        <v>1455</v>
       </c>
       <c r="W198" s="5" t="n">
         <v>0</v>
@@ -15663,10 +15693,10 @@
         <v>23</v>
       </c>
       <c r="U199" s="5" t="n">
-        <v>750</v>
+        <v>0</v>
       </c>
       <c r="V199" s="5" t="n">
-        <v>2204</v>
+        <v>1477</v>
       </c>
       <c r="W199" s="5" t="n">
         <v>0</v>
@@ -15740,10 +15770,10 @@
         <v>16</v>
       </c>
       <c r="U200" s="5" t="n">
-        <v>539</v>
+        <v>0</v>
       </c>
       <c r="V200" s="5" t="n">
-        <v>1583</v>
+        <v>1060</v>
       </c>
       <c r="W200" s="5" t="n">
         <v>0</v>
@@ -15817,10 +15847,10 @@
         <v>22</v>
       </c>
       <c r="U201" s="5" t="n">
-        <v>707</v>
+        <v>0</v>
       </c>
       <c r="V201" s="5" t="n">
-        <v>2077</v>
+        <v>1392</v>
       </c>
       <c r="W201" s="5" t="n">
         <v>0</v>
@@ -15894,10 +15924,10 @@
         <v>4</v>
       </c>
       <c r="U202" s="5" t="n">
-        <v>742</v>
+        <v>0</v>
       </c>
       <c r="V202" s="5" t="n">
-        <v>2258</v>
+        <v>1520</v>
       </c>
       <c r="W202" s="5" t="n">
         <v>0</v>
@@ -15971,10 +16001,10 @@
         <v>0</v>
       </c>
       <c r="U203" s="5" t="n">
-        <v>792</v>
+        <v>0</v>
       </c>
       <c r="V203" s="5" t="n">
-        <v>2376</v>
+        <v>1584</v>
       </c>
       <c r="W203" s="5" t="n">
         <v>0</v>
@@ -16051,7 +16081,7 @@
         <v>278</v>
       </c>
       <c r="V204" s="5" t="n">
-        <v>820</v>
+        <v>827</v>
       </c>
       <c r="W204" s="5" t="n">
         <v>0</v>
@@ -16125,10 +16155,10 @@
         <v>22</v>
       </c>
       <c r="U205" s="5" t="n">
-        <v>965</v>
+        <v>0</v>
       </c>
       <c r="V205" s="5" t="n">
-        <v>2847</v>
+        <v>1904</v>
       </c>
       <c r="W205" s="5" t="n">
         <v>0</v>
@@ -16202,10 +16232,10 @@
         <v>29</v>
       </c>
       <c r="U206" s="5" t="n">
-        <v>724</v>
+        <v>0</v>
       </c>
       <c r="V206" s="5" t="n">
-        <v>2114</v>
+        <v>1419</v>
       </c>
       <c r="W206" s="5" t="n">
         <v>0</v>
@@ -16279,10 +16309,10 @@
         <v>24</v>
       </c>
       <c r="U207" s="5" t="n">
-        <v>763</v>
+        <v>0</v>
       </c>
       <c r="V207" s="5" t="n">
-        <v>2241</v>
+        <v>1502</v>
       </c>
       <c r="W207" s="5" t="n">
         <v>0</v>
@@ -16356,10 +16386,10 @@
         <v>36</v>
       </c>
       <c r="U208" s="5" t="n">
-        <v>886</v>
+        <v>0</v>
       </c>
       <c r="V208" s="5" t="n">
-        <v>2586</v>
+        <v>1736</v>
       </c>
       <c r="W208" s="5" t="n">
         <v>0</v>
@@ -16433,10 +16463,10 @@
         <v>8</v>
       </c>
       <c r="U209" s="5" t="n">
-        <v>695</v>
+        <v>0</v>
       </c>
       <c r="V209" s="5" t="n">
-        <v>2025</v>
+        <v>1338</v>
       </c>
       <c r="W209" s="5" t="n">
         <v>0</v>
@@ -16510,10 +16540,10 @@
         <v>32</v>
       </c>
       <c r="U210" s="5" t="n">
-        <v>692</v>
+        <v>0</v>
       </c>
       <c r="V210" s="5" t="n">
-        <v>2012</v>
+        <v>1352</v>
       </c>
       <c r="W210" s="5" t="n">
         <v>0</v>
@@ -16590,7 +16620,7 @@
         <v>431</v>
       </c>
       <c r="V211" s="5" t="n">
-        <v>1267</v>
+        <v>1280</v>
       </c>
       <c r="W211" s="5" t="n">
         <v>0</v>
@@ -16664,10 +16694,10 @@
         <v>10</v>
       </c>
       <c r="U212" s="5" t="n">
-        <v>514</v>
+        <v>0</v>
       </c>
       <c r="V212" s="5" t="n">
-        <v>1522</v>
+        <v>1018</v>
       </c>
       <c r="W212" s="5" t="n">
         <v>0</v>
@@ -16741,10 +16771,10 @@
         <v>5</v>
       </c>
       <c r="U213" s="5" t="n">
-        <v>739</v>
+        <v>0</v>
       </c>
       <c r="V213" s="5" t="n">
-        <v>2207</v>
+        <v>1473</v>
       </c>
       <c r="W213" s="5" t="n">
         <v>0</v>
@@ -16818,10 +16848,10 @@
         <v>15</v>
       </c>
       <c r="U214" s="5" t="n">
-        <v>743</v>
+        <v>0</v>
       </c>
       <c r="V214" s="5" t="n">
-        <v>2239</v>
+        <v>1511</v>
       </c>
       <c r="W214" s="5" t="n">
         <v>0</v>
@@ -16895,10 +16925,10 @@
         <v>14</v>
       </c>
       <c r="U215" s="5" t="n">
-        <v>894</v>
+        <v>0</v>
       </c>
       <c r="V215" s="5" t="n">
-        <v>2654</v>
+        <v>1774</v>
       </c>
       <c r="W215" s="5" t="n">
         <v>0</v>
@@ -16972,10 +17002,10 @@
         <v>24</v>
       </c>
       <c r="U216" s="5" t="n">
-        <v>831</v>
+        <v>0</v>
       </c>
       <c r="V216" s="5" t="n">
-        <v>2444</v>
+        <v>1637</v>
       </c>
       <c r="W216" s="5" t="n">
         <v>0</v>
@@ -17052,7 +17082,7 @@
         <v>476</v>
       </c>
       <c r="V217" s="5" t="n">
-        <v>1399</v>
+        <v>1413</v>
       </c>
       <c r="W217" s="5" t="n">
         <v>0</v>
@@ -17126,10 +17156,10 @@
         <v>21</v>
       </c>
       <c r="U218" s="5" t="n">
-        <v>558</v>
+        <v>0</v>
       </c>
       <c r="V218" s="5" t="n">
-        <v>1632</v>
+        <v>1095</v>
       </c>
       <c r="W218" s="5" t="n">
         <v>0</v>
@@ -17203,10 +17233,10 @@
         <v>11</v>
       </c>
       <c r="U219" s="5" t="n">
-        <v>904</v>
+        <v>0</v>
       </c>
       <c r="V219" s="5" t="n">
-        <v>2730</v>
+        <v>1837</v>
       </c>
       <c r="W219" s="5" t="n">
         <v>0</v>
@@ -17274,7 +17304,7 @@
         <v>17</v>
       </c>
       <c r="S220" s="5" t="n">
-        <v>18</v>
+        <v>152</v>
       </c>
       <c r="T220" s="5" t="n">
         <v>19</v>
@@ -17283,7 +17313,7 @@
         <v>20</v>
       </c>
       <c r="V220" s="5" t="n">
-        <v>21</v>
+        <v>191</v>
       </c>
       <c r="W220" s="5" t="n">
         <v>0</v>
@@ -17360,7 +17390,7 @@
         <v>410</v>
       </c>
       <c r="V221" s="5" t="n">
-        <v>1194</v>
+        <v>1207</v>
       </c>
       <c r="W221" s="5" t="n">
         <v>0</v>
@@ -17434,10 +17464,10 @@
         <v>7</v>
       </c>
       <c r="U222" s="5" t="n">
-        <v>772</v>
+        <v>0</v>
       </c>
       <c r="V222" s="5" t="n">
-        <v>2302</v>
+        <v>1537</v>
       </c>
       <c r="W222" s="5" t="n">
         <v>0</v>
@@ -17511,10 +17541,10 @@
         <v>14</v>
       </c>
       <c r="U223" s="5" t="n">
-        <v>823</v>
+        <v>0</v>
       </c>
       <c r="V223" s="5" t="n">
-        <v>2441</v>
+        <v>1632</v>
       </c>
       <c r="W223" s="5" t="n">
         <v>0</v>
@@ -17588,10 +17618,10 @@
         <v>25</v>
       </c>
       <c r="U224" s="5" t="n">
-        <v>623</v>
+        <v>0</v>
       </c>
       <c r="V224" s="5" t="n">
-        <v>1819</v>
+        <v>1221</v>
       </c>
       <c r="W224" s="5" t="n">
         <v>0</v>
@@ -17665,10 +17695,10 @@
         <v>8</v>
       </c>
       <c r="U225" s="5" t="n">
-        <v>622</v>
+        <v>0</v>
       </c>
       <c r="V225" s="5" t="n">
-        <v>1890</v>
+        <v>1276</v>
       </c>
       <c r="W225" s="5" t="n">
         <v>0</v>
@@ -17742,10 +17772,10 @@
         <v>7</v>
       </c>
       <c r="U226" s="5" t="n">
-        <v>959</v>
+        <v>0</v>
       </c>
       <c r="V226" s="5" t="n">
-        <v>2863</v>
+        <v>1911</v>
       </c>
       <c r="W226" s="5" t="n">
         <v>4</v>
@@ -17819,10 +17849,10 @@
         <v>12</v>
       </c>
       <c r="U227" s="5" t="n">
-        <v>930</v>
+        <v>0</v>
       </c>
       <c r="V227" s="5" t="n">
-        <v>2806</v>
+        <v>1888</v>
       </c>
       <c r="W227" s="5" t="n">
         <v>1</v>
@@ -17896,10 +17926,10 @@
         <v>10</v>
       </c>
       <c r="U228" s="5" t="n">
-        <v>817</v>
+        <v>0</v>
       </c>
       <c r="V228" s="5" t="n">
-        <v>2431</v>
+        <v>1624</v>
       </c>
       <c r="W228" s="5" t="n">
         <v>0</v>
@@ -17973,10 +18003,10 @@
         <v>14</v>
       </c>
       <c r="U229" s="5" t="n">
-        <v>763</v>
+        <v>0</v>
       </c>
       <c r="V229" s="5" t="n">
-        <v>2264</v>
+        <v>1515</v>
       </c>
       <c r="W229" s="5" t="n">
         <v>0</v>
@@ -18050,10 +18080,10 @@
         <v>12</v>
       </c>
       <c r="U230" s="5" t="n">
-        <v>676</v>
+        <v>0</v>
       </c>
       <c r="V230" s="5" t="n">
-        <v>2004</v>
+        <v>1340</v>
       </c>
       <c r="W230" s="5" t="n">
         <v>0</v>
@@ -18127,10 +18157,10 @@
         <v>17</v>
       </c>
       <c r="U231" s="5" t="n">
-        <v>913</v>
+        <v>0</v>
       </c>
       <c r="V231" s="5" t="n">
-        <v>2695</v>
+        <v>1799</v>
       </c>
       <c r="W231" s="5" t="n">
         <v>0</v>
@@ -18204,10 +18234,10 @@
         <v>35</v>
       </c>
       <c r="U232" s="5" t="n">
-        <v>830</v>
+        <v>0</v>
       </c>
       <c r="V232" s="5" t="n">
-        <v>2420</v>
+        <v>1625</v>
       </c>
       <c r="W232" s="5" t="n">
         <v>0</v>
@@ -18284,7 +18314,7 @@
         <v>353</v>
       </c>
       <c r="V233" s="5" t="n">
-        <v>1052</v>
+        <v>1057</v>
       </c>
       <c r="W233" s="5" t="n">
         <v>0</v>
@@ -18358,10 +18388,10 @@
         <v>14</v>
       </c>
       <c r="U234" s="5" t="n">
-        <v>858</v>
+        <v>0</v>
       </c>
       <c r="V234" s="5" t="n">
-        <v>2546</v>
+        <v>1702</v>
       </c>
       <c r="W234" s="5" t="n">
         <v>0</v>
@@ -18435,10 +18465,10 @@
         <v>13</v>
       </c>
       <c r="U235" s="5" t="n">
-        <v>797</v>
+        <v>0</v>
       </c>
       <c r="V235" s="5" t="n">
-        <v>2365</v>
+        <v>1581</v>
       </c>
       <c r="W235" s="5" t="n">
         <v>0</v>
@@ -18512,10 +18542,10 @@
         <v>11</v>
       </c>
       <c r="U236" s="5" t="n">
-        <v>700</v>
+        <v>0</v>
       </c>
       <c r="V236" s="5" t="n">
-        <v>2078</v>
+        <v>1389</v>
       </c>
       <c r="W236" s="5" t="n">
         <v>4</v>
@@ -18592,7 +18622,7 @@
         <v>344</v>
       </c>
       <c r="V237" s="5" t="n">
-        <v>1022</v>
+        <v>1027</v>
       </c>
       <c r="W237" s="5" t="n">
         <v>0</v>
@@ -18666,10 +18696,10 @@
         <v>12</v>
       </c>
       <c r="U238" s="5" t="n">
-        <v>650</v>
+        <v>0</v>
       </c>
       <c r="V238" s="5" t="n">
-        <v>1926</v>
+        <v>1288</v>
       </c>
       <c r="W238" s="5" t="n">
         <v>0</v>
@@ -18743,10 +18773,10 @@
         <v>3</v>
       </c>
       <c r="U239" s="5" t="n">
-        <v>604</v>
+        <v>0</v>
       </c>
       <c r="V239" s="5" t="n">
-        <v>1806</v>
+        <v>1205</v>
       </c>
       <c r="W239" s="5" t="n">
         <v>0</v>
@@ -18820,10 +18850,10 @@
         <v>12</v>
       </c>
       <c r="U240" s="5" t="n">
-        <v>802</v>
+        <v>0</v>
       </c>
       <c r="V240" s="5" t="n">
-        <v>2422</v>
+        <v>1632</v>
       </c>
       <c r="W240" s="5" t="n">
         <v>4</v>
@@ -18897,10 +18927,10 @@
         <v>21</v>
       </c>
       <c r="U241" s="5" t="n">
-        <v>898</v>
+        <v>0</v>
       </c>
       <c r="V241" s="5" t="n">
-        <v>2652</v>
+        <v>1775</v>
       </c>
       <c r="W241" s="5" t="n">
         <v>4</v>
@@ -18974,10 +19004,10 @@
         <v>32</v>
       </c>
       <c r="U242" s="5" t="n">
-        <v>870</v>
+        <v>0</v>
       </c>
       <c r="V242" s="5" t="n">
-        <v>2506</v>
+        <v>1668</v>
       </c>
       <c r="W242" s="5" t="n">
         <v>4</v>
@@ -19052,10 +19082,10 @@
         <v>12</v>
       </c>
       <c r="U243" s="5" t="n">
-        <v>768</v>
+        <v>0</v>
       </c>
       <c r="V243" s="5" t="n">
-        <v>2283</v>
+        <v>1527</v>
       </c>
       <c r="W243" s="5" t="n">
         <v>0</v>
@@ -19132,7 +19162,7 @@
         <v>479</v>
       </c>
       <c r="V244" s="5" t="n">
-        <v>1427</v>
+        <v>1432</v>
       </c>
       <c r="W244" s="5" t="n">
         <v>0</v>
@@ -19206,10 +19236,10 @@
         <v>9</v>
       </c>
       <c r="U245" s="5" t="n">
-        <v>626</v>
+        <v>0</v>
       </c>
       <c r="V245" s="5" t="n">
-        <v>1863</v>
+        <v>1246</v>
       </c>
       <c r="W245" s="5" t="n">
         <v>4</v>
@@ -19286,7 +19316,7 @@
         <v>495</v>
       </c>
       <c r="V246" s="5" t="n">
-        <v>1465</v>
+        <v>1475</v>
       </c>
       <c r="W246" s="5" t="n">
         <v>0</v>
@@ -19360,10 +19390,10 @@
         <v>19</v>
       </c>
       <c r="U247" s="5" t="n">
-        <v>530</v>
+        <v>0</v>
       </c>
       <c r="V247" s="5" t="n">
-        <v>1552</v>
+        <v>1041</v>
       </c>
       <c r="W247" s="5" t="n">
         <v>0</v>
@@ -19440,7 +19470,7 @@
         <v>471</v>
       </c>
       <c r="V248" s="5" t="n">
-        <v>1463</v>
+        <v>1472</v>
       </c>
       <c r="W248" s="5" t="n">
         <v>4</v>
@@ -19517,7 +19547,7 @@
         <v>461</v>
       </c>
       <c r="V249" s="5" t="n">
-        <v>1374</v>
+        <v>1380</v>
       </c>
       <c r="W249" s="5" t="n">
         <v>1</v>
@@ -19586,7 +19616,7 @@
         <v>17</v>
       </c>
       <c r="S250" s="5" t="n">
-        <v>18</v>
+        <v>150</v>
       </c>
       <c r="T250" s="5" t="n">
         <v>19</v>
@@ -19595,7 +19625,7 @@
         <v>20</v>
       </c>
       <c r="V250" s="5" t="n">
-        <v>21</v>
+        <v>189</v>
       </c>
       <c r="W250" s="5" t="n">
         <v>0</v>
@@ -19669,10 +19699,10 @@
         <v>25</v>
       </c>
       <c r="U251" s="5" t="n">
-        <v>809</v>
+        <v>0</v>
       </c>
       <c r="V251" s="5" t="n">
-        <v>2377</v>
+        <v>1593</v>
       </c>
       <c r="W251" s="5" t="n">
         <v>4</v>
@@ -19746,10 +19776,10 @@
         <v>27</v>
       </c>
       <c r="U252" s="5" t="n">
-        <v>818</v>
+        <v>0</v>
       </c>
       <c r="V252" s="5" t="n">
-        <v>2400</v>
+        <v>1609</v>
       </c>
       <c r="W252" s="5" t="n">
         <v>4</v>
@@ -19823,10 +19853,10 @@
         <v>16</v>
       </c>
       <c r="U253" s="5" t="n">
-        <v>796</v>
+        <v>0</v>
       </c>
       <c r="V253" s="5" t="n">
-        <v>2726</v>
+        <v>1946</v>
       </c>
       <c r="W253" s="5" t="n">
         <v>4</v>
@@ -19900,10 +19930,10 @@
         <v>25</v>
       </c>
       <c r="U254" s="5" t="n">
-        <v>523</v>
+        <v>0</v>
       </c>
       <c r="V254" s="5" t="n">
-        <v>1519</v>
+        <v>1021</v>
       </c>
       <c r="W254" s="5" t="n">
         <v>3</v>
@@ -19980,7 +20010,7 @@
         <v>493</v>
       </c>
       <c r="V255" s="5" t="n">
-        <v>1449</v>
+        <v>1464</v>
       </c>
       <c r="W255" s="5" t="n">
         <v>0</v>
@@ -20054,10 +20084,10 @@
         <v>28</v>
       </c>
       <c r="U256" s="5" t="n">
-        <v>932</v>
+        <v>0</v>
       </c>
       <c r="V256" s="5" t="n">
-        <v>3143</v>
+        <v>2239</v>
       </c>
       <c r="W256" s="5" t="n">
         <v>0</v>
@@ -20131,10 +20161,10 @@
         <v>17</v>
       </c>
       <c r="U257" s="5" t="n">
-        <v>858</v>
+        <v>0</v>
       </c>
       <c r="V257" s="5" t="n">
-        <v>2543</v>
+        <v>1702</v>
       </c>
       <c r="W257" s="5" t="n">
         <v>4</v>
@@ -20208,10 +20238,10 @@
         <v>20</v>
       </c>
       <c r="U258" s="5" t="n">
-        <v>527</v>
+        <v>0</v>
       </c>
       <c r="V258" s="5" t="n">
-        <v>1541</v>
+        <v>1034</v>
       </c>
       <c r="W258" s="5" t="n">
         <v>0</v>
@@ -20288,7 +20318,7 @@
         <v>448</v>
       </c>
       <c r="V259" s="5" t="n">
-        <v>1613</v>
+        <v>1624</v>
       </c>
       <c r="W259" s="5" t="n">
         <v>0</v>
@@ -20362,10 +20392,10 @@
         <v>26</v>
       </c>
       <c r="U260" s="5" t="n">
-        <v>788</v>
+        <v>0</v>
       </c>
       <c r="V260" s="5" t="n">
-        <v>2382</v>
+        <v>1620</v>
       </c>
       <c r="W260" s="5" t="n">
         <v>4</v>
@@ -20439,10 +20469,10 @@
         <v>23</v>
       </c>
       <c r="U261" s="5" t="n">
-        <v>709</v>
+        <v>0</v>
       </c>
       <c r="V261" s="5" t="n">
-        <v>2081</v>
+        <v>1395</v>
       </c>
       <c r="W261" s="5" t="n">
         <v>3</v>
@@ -20516,10 +20546,10 @@
         <v>12</v>
       </c>
       <c r="U262" s="5" t="n">
-        <v>798</v>
+        <v>0</v>
       </c>
       <c r="V262" s="5" t="n">
-        <v>2</v>
+        <v>1580</v>
       </c>
       <c r="W262" s="5" t="n">
         <v>4</v>
@@ -20593,10 +20623,10 @@
         <v>13</v>
       </c>
       <c r="U263" s="5" t="n">
-        <v>773</v>
+        <v>0</v>
       </c>
       <c r="V263" s="5" t="n">
-        <v>2293</v>
+        <v>1533</v>
       </c>
       <c r="W263" s="5" t="n">
         <v>7</v>
@@ -20616,7 +20646,7 @@
         </is>
       </c>
       <c r="C264" s="5" t="n">
-        <v>4175</v>
+        <v>0</v>
       </c>
       <c r="D264" s="5" t="n">
         <v>5</v>
@@ -20664,16 +20694,16 @@
         <v>585</v>
       </c>
       <c r="S264" s="5" t="n">
-        <v>5170</v>
+        <v>995</v>
       </c>
       <c r="T264" s="5" t="n">
         <v>22</v>
       </c>
       <c r="U264" s="5" t="n">
-        <v>607</v>
+        <v>0</v>
       </c>
       <c r="V264" s="5" t="n">
-        <v>5777</v>
+        <v>1017</v>
       </c>
       <c r="W264" s="5" t="n">
         <v>0</v>
@@ -20747,10 +20777,10 @@
         <v>20</v>
       </c>
       <c r="U265" s="5" t="n">
-        <v>592</v>
+        <v>0</v>
       </c>
       <c r="V265" s="5" t="n">
-        <v>1736</v>
+        <v>1164</v>
       </c>
       <c r="W265" s="5" t="n">
         <v>0</v>
@@ -20824,10 +20854,10 @@
         <v>11</v>
       </c>
       <c r="U266" s="5" t="n">
-        <v>574</v>
+        <v>0</v>
       </c>
       <c r="V266" s="5" t="n">
-        <v>2</v>
+        <v>1180</v>
       </c>
       <c r="W266" s="5" t="n">
         <v>0</v>
@@ -20901,10 +20931,10 @@
         <v>12</v>
       </c>
       <c r="U267" s="5" t="n">
-        <v>690</v>
+        <v>0</v>
       </c>
       <c r="V267" s="5" t="n">
-        <v>2046</v>
+        <v>1368</v>
       </c>
       <c r="W267" s="5" t="n">
         <v>0</v>
@@ -20978,10 +21008,10 @@
         <v>13</v>
       </c>
       <c r="U268" s="5" t="n">
-        <v>679</v>
+        <v>0</v>
       </c>
       <c r="V268" s="5" t="n">
-        <v>1981</v>
+        <v>1315</v>
       </c>
       <c r="W268" s="5" t="n">
         <v>0</v>
@@ -21058,7 +21088,7 @@
         <v>41</v>
       </c>
       <c r="V269" s="5" t="n">
-        <v>1109</v>
+        <v>1119</v>
       </c>
       <c r="W269" s="5" t="n">
         <v>0</v>
@@ -21132,10 +21162,10 @@
         <v>16</v>
       </c>
       <c r="U270" s="5" t="n">
-        <v>743</v>
+        <v>0</v>
       </c>
       <c r="V270" s="5" t="n">
-        <v>2192</v>
+        <v>1465</v>
       </c>
       <c r="W270" s="5" t="n">
         <v>0</v>
@@ -21209,10 +21239,10 @@
         <v>14</v>
       </c>
       <c r="U271" s="5" t="n">
-        <v>850</v>
+        <v>0</v>
       </c>
       <c r="V271" s="5" t="n">
-        <v>2524</v>
+        <v>1688</v>
       </c>
       <c r="W271" s="5" t="n">
         <v>0</v>
@@ -21286,10 +21316,10 @@
         <v>5</v>
       </c>
       <c r="U272" s="5" t="n">
-        <v>600</v>
+        <v>0</v>
       </c>
       <c r="V272" s="5" t="n">
-        <v>2236</v>
+        <v>1641</v>
       </c>
       <c r="W272" s="5" t="n">
         <v>0</v>
@@ -21366,7 +21396,7 @@
         <v>475</v>
       </c>
       <c r="V273" s="5" t="n">
-        <v>1554</v>
+        <v>1564</v>
       </c>
       <c r="W273" s="5" t="n">
         <v>0</v>
@@ -21440,10 +21470,10 @@
         <v>13</v>
       </c>
       <c r="U274" s="5" t="n">
-        <v>797</v>
+        <v>0</v>
       </c>
       <c r="V274" s="5" t="n">
-        <v>2367</v>
+        <v>1583</v>
       </c>
       <c r="W274" s="5" t="n">
         <v>0</v>
@@ -21517,10 +21547,10 @@
         <v>13</v>
       </c>
       <c r="U275" s="5" t="n">
-        <v>507</v>
+        <v>0</v>
       </c>
       <c r="V275" s="5" t="n">
-        <v>1527</v>
+        <v>1033</v>
       </c>
       <c r="W275" s="5" t="n">
         <v>0</v>
@@ -21597,7 +21627,7 @@
         <v>403</v>
       </c>
       <c r="V276" s="5" t="n">
-        <v>1188</v>
+        <v>1200</v>
       </c>
       <c r="W276" s="5" t="n">
         <v>0</v>
@@ -21671,10 +21701,10 @@
         <v>12</v>
       </c>
       <c r="U277" s="5" t="n">
-        <v>510</v>
+        <v>0</v>
       </c>
       <c r="V277" s="5" t="n">
-        <v>1506</v>
+        <v>1008</v>
       </c>
       <c r="W277" s="5" t="n">
         <v>0</v>
@@ -21748,10 +21778,10 @@
         <v>413</v>
       </c>
       <c r="U278" s="5" t="n">
-        <v>560</v>
+        <v>0</v>
       </c>
       <c r="V278" s="5" t="n">
-        <v>1695</v>
+        <v>1548</v>
       </c>
       <c r="W278" s="5" t="n">
         <v>0</v>
@@ -21828,7 +21858,7 @@
         <v>466</v>
       </c>
       <c r="V279" s="5" t="n">
-        <v>1361</v>
+        <v>1381</v>
       </c>
       <c r="W279" s="5" t="n">
         <v>0</v>
@@ -21902,10 +21932,10 @@
         <v>414</v>
       </c>
       <c r="U280" s="5" t="n">
-        <v>772</v>
+        <v>0</v>
       </c>
       <c r="V280" s="5" t="n">
-        <v>2465</v>
+        <v>2107</v>
       </c>
       <c r="W280" s="5" t="n">
         <v>0</v>
@@ -21979,10 +22009,10 @@
         <v>15</v>
       </c>
       <c r="U281" s="5" t="n">
-        <v>883</v>
+        <v>0</v>
       </c>
       <c r="V281" s="5" t="n">
-        <v>2635</v>
+        <v>1767</v>
       </c>
       <c r="W281" s="5" t="n">
         <v>0</v>
@@ -22056,10 +22086,10 @@
         <v>13</v>
       </c>
       <c r="U282" s="5" t="n">
-        <v>811</v>
+        <v>0</v>
       </c>
       <c r="V282" s="5" t="n">
-        <v>1949</v>
+        <v>1151</v>
       </c>
       <c r="W282" s="5" t="n">
         <v>0</v>
@@ -22133,10 +22163,10 @@
         <v>415</v>
       </c>
       <c r="U283" s="5" t="n">
-        <v>590</v>
+        <v>0</v>
       </c>
       <c r="V283" s="5" t="n">
-        <v>1283</v>
+        <v>1108</v>
       </c>
       <c r="W283" s="5" t="n">
         <v>0</v>
@@ -22204,7 +22234,7 @@
         <v>17</v>
       </c>
       <c r="S284" s="5" t="n">
-        <v>3</v>
+        <v>145</v>
       </c>
       <c r="T284" s="5" t="n">
         <v>3</v>
@@ -22213,7 +22243,7 @@
         <v>20</v>
       </c>
       <c r="V284" s="5" t="n">
-        <v>21</v>
+        <v>168</v>
       </c>
       <c r="W284" s="5" t="n">
         <v>0</v>
@@ -22287,10 +22317,10 @@
         <v>16</v>
       </c>
       <c r="U285" s="5" t="n">
-        <v>533</v>
+        <v>0</v>
       </c>
       <c r="V285" s="5" t="n">
-        <v>1559</v>
+        <v>1042</v>
       </c>
       <c r="W285" s="5" t="n">
         <v>0</v>
@@ -22364,10 +22394,10 @@
         <v>42</v>
       </c>
       <c r="U286" s="5" t="n">
-        <v>511</v>
+        <v>0</v>
       </c>
       <c r="V286" s="5" t="n">
-        <v>1553</v>
+        <v>1084</v>
       </c>
       <c r="W286" s="5" t="n">
         <v>0</v>
@@ -22444,7 +22474,7 @@
         <v>441</v>
       </c>
       <c r="V287" s="5" t="n">
-        <v>1314</v>
+        <v>1315</v>
       </c>
       <c r="W287" s="5" t="n">
         <v>0</v>
@@ -22518,10 +22548,10 @@
         <v>4</v>
       </c>
       <c r="U288" s="5" t="n">
-        <v>535</v>
+        <v>0</v>
       </c>
       <c r="V288" s="5" t="n">
-        <v>1588</v>
+        <v>1057</v>
       </c>
       <c r="W288" s="5" t="n">
         <v>0</v>
@@ -22595,10 +22625,10 @@
         <v>14</v>
       </c>
       <c r="U289" s="5" t="n">
-        <v>618</v>
+        <v>0</v>
       </c>
       <c r="V289" s="5" t="n">
-        <v>1826</v>
+        <v>1222</v>
       </c>
       <c r="W289" s="5" t="n">
         <v>0</v>
@@ -22672,10 +22702,10 @@
         <v>17</v>
       </c>
       <c r="U290" s="5" t="n">
-        <v>735</v>
+        <v>0</v>
       </c>
       <c r="V290" s="5" t="n">
-        <v>2168</v>
+        <v>1450</v>
       </c>
       <c r="W290" s="5" t="n">
         <v>0</v>
@@ -22749,10 +22779,10 @@
         <v>6</v>
       </c>
       <c r="U291" s="5" t="n">
-        <v>550</v>
+        <v>0</v>
       </c>
       <c r="V291" s="5" t="n">
-        <v>1641</v>
+        <v>1097</v>
       </c>
       <c r="W291" s="5" t="n">
         <v>0</v>
@@ -22826,10 +22856,10 @@
         <v>19</v>
       </c>
       <c r="U292" s="5" t="n">
-        <v>748</v>
+        <v>0</v>
       </c>
       <c r="V292" s="5" t="n">
-        <v>2196</v>
+        <v>1467</v>
       </c>
       <c r="W292" s="5" t="n">
         <v>0</v>
@@ -22903,10 +22933,10 @@
         <v>16</v>
       </c>
       <c r="U293" s="5" t="n">
-        <v>831</v>
+        <v>0</v>
       </c>
       <c r="V293" s="5" t="n">
-        <v>2454</v>
+        <v>1639</v>
       </c>
       <c r="W293" s="5" t="n">
         <v>0</v>
@@ -22980,10 +23010,10 @@
         <v>20</v>
       </c>
       <c r="U294" s="5" t="n">
-        <v>818</v>
+        <v>0</v>
       </c>
       <c r="V294" s="5" t="n">
-        <v>2414</v>
+        <v>1616</v>
       </c>
       <c r="W294" s="5" t="n">
         <v>0</v>
@@ -23057,10 +23087,10 @@
         <v>14</v>
       </c>
       <c r="U295" s="5" t="n">
-        <v>720</v>
+        <v>0</v>
       </c>
       <c r="V295" s="5" t="n">
-        <v>2125</v>
+        <v>1419</v>
       </c>
       <c r="W295" s="5" t="n">
         <v>0</v>
@@ -23134,10 +23164,10 @@
         <v>4</v>
       </c>
       <c r="U296" s="5" t="n">
-        <v>564</v>
+        <v>0</v>
       </c>
       <c r="V296" s="5" t="n">
-        <v>1713</v>
+        <v>1153</v>
       </c>
       <c r="W296" s="5" t="n">
         <v>0</v>
@@ -23211,10 +23241,10 @@
         <v>9</v>
       </c>
       <c r="U297" s="5" t="n">
-        <v>553</v>
+        <v>0</v>
       </c>
       <c r="V297" s="5" t="n">
-        <v>1641</v>
+        <v>1097</v>
       </c>
       <c r="W297" s="5" t="n">
         <v>0</v>
@@ -23288,10 +23318,10 @@
         <v>12</v>
       </c>
       <c r="U298" s="5" t="n">
-        <v>824</v>
+        <v>0</v>
       </c>
       <c r="V298" s="5" t="n">
-        <v>2438</v>
+        <v>1626</v>
       </c>
       <c r="W298" s="5" t="n">
         <v>0</v>
@@ -23365,10 +23395,10 @@
         <v>14</v>
       </c>
       <c r="U299" s="5" t="n">
-        <v>770</v>
+        <v>0</v>
       </c>
       <c r="V299" s="5" t="n">
-        <v>2275</v>
+        <v>1519</v>
       </c>
       <c r="W299" s="5" t="n">
         <v>0</v>
@@ -23442,10 +23472,10 @@
         <v>17</v>
       </c>
       <c r="U300" s="5" t="n">
-        <v>912</v>
+        <v>0</v>
       </c>
       <c r="V300" s="5" t="n">
-        <v>2702</v>
+        <v>1807</v>
       </c>
       <c r="W300" s="5" t="n">
         <v>1</v>
@@ -23513,7 +23543,7 @@
         <v>0</v>
       </c>
       <c r="S301" s="5" t="n">
-        <v>579</v>
+        <v>577</v>
       </c>
       <c r="T301" s="5" t="n">
         <v>0</v>
@@ -23522,7 +23552,7 @@
         <v>6</v>
       </c>
       <c r="V301" s="5" t="n">
-        <v>585</v>
+        <v>583</v>
       </c>
       <c r="W301" s="5" t="n">
         <v>0</v>
@@ -23590,7 +23620,7 @@
         <v>0</v>
       </c>
       <c r="S302" s="5" t="n">
-        <v>534</v>
+        <v>531</v>
       </c>
       <c r="T302" s="5" t="n">
         <v>0</v>
@@ -23599,7 +23629,7 @@
         <v>10</v>
       </c>
       <c r="V302" s="5" t="n">
-        <v>544</v>
+        <v>541</v>
       </c>
       <c r="W302" s="5" t="n">
         <v>0</v>
@@ -23821,7 +23851,7 @@
         <v>0</v>
       </c>
       <c r="S305" s="5" t="n">
-        <v>586</v>
+        <v>582</v>
       </c>
       <c r="T305" s="5" t="n">
         <v>0</v>
@@ -23830,7 +23860,7 @@
         <v>12</v>
       </c>
       <c r="V305" s="5" t="n">
-        <v>598</v>
+        <v>594</v>
       </c>
       <c r="W305" s="5" t="n">
         <v>0</v>
@@ -23841,267 +23871,267 @@
       </c>
     </row>
     <row r="306">
-      <c r="A306" s="9" t="inlineStr">
+      <c r="A306" s="18" t="inlineStr">
         <is>
           <t>TOTAL EVM VOTES</t>
         </is>
       </c>
-      <c r="B306" s="10" t="inlineStr"/>
-      <c r="C306" s="11">
+      <c r="B306" s="19" t="inlineStr"/>
+      <c r="C306" s="20">
         <f>SUM(C6:C305)</f>
         <v/>
       </c>
-      <c r="D306" s="11">
+      <c r="D306" s="20">
         <f>SUM(D6:D305)</f>
         <v/>
       </c>
-      <c r="E306" s="11">
+      <c r="E306" s="20">
         <f>SUM(E6:E305)</f>
         <v/>
       </c>
-      <c r="F306" s="11">
+      <c r="F306" s="20">
         <f>SUM(F6:F305)</f>
         <v/>
       </c>
-      <c r="G306" s="11">
+      <c r="G306" s="20">
         <f>SUM(G6:G305)</f>
         <v/>
       </c>
-      <c r="H306" s="11">
+      <c r="H306" s="20">
         <f>SUM(H6:H305)</f>
         <v/>
       </c>
-      <c r="I306" s="11">
+      <c r="I306" s="20">
         <f>SUM(I6:I305)</f>
         <v/>
       </c>
-      <c r="J306" s="11">
+      <c r="J306" s="20">
         <f>SUM(J6:J305)</f>
         <v/>
       </c>
-      <c r="K306" s="11">
+      <c r="K306" s="20">
         <f>SUM(K6:K305)</f>
         <v/>
       </c>
-      <c r="L306" s="11">
+      <c r="L306" s="20">
         <f>SUM(L6:L305)</f>
         <v/>
       </c>
-      <c r="M306" s="11">
+      <c r="M306" s="20">
         <f>SUM(M6:M305)</f>
         <v/>
       </c>
-      <c r="N306" s="11">
+      <c r="N306" s="20">
         <f>SUM(N6:N305)</f>
         <v/>
       </c>
-      <c r="O306" s="11">
+      <c r="O306" s="20">
         <f>SUM(O6:O305)</f>
         <v/>
       </c>
-      <c r="P306" s="11">
+      <c r="P306" s="20">
         <f>SUM(P6:P305)</f>
         <v/>
       </c>
-      <c r="Q306" s="11">
+      <c r="Q306" s="20">
         <f>SUM(Q6:Q305)</f>
         <v/>
       </c>
-      <c r="R306" s="11">
+      <c r="R306" s="20">
         <f>SUM(R6:R305)</f>
         <v/>
       </c>
-      <c r="S306" s="11">
+      <c r="S306" s="20">
         <f>SUM(S6:S305)</f>
         <v/>
       </c>
-      <c r="T306" s="11">
+      <c r="T306" s="20">
         <f>SUM(T6:T305)</f>
         <v/>
       </c>
-      <c r="U306" s="11">
+      <c r="U306" s="20">
         <f>SUM(U6:U305)</f>
         <v/>
       </c>
-      <c r="V306" s="11">
+      <c r="V306" s="20">
         <f>SUM(V6:V305)</f>
         <v/>
       </c>
-      <c r="W306" s="11">
+      <c r="W306" s="20">
         <f>SUM(W6:W305)</f>
         <v/>
       </c>
-      <c r="X306" s="11">
+      <c r="X306" s="20">
         <f>SUM(X6:X305)</f>
         <v/>
       </c>
     </row>
     <row r="307">
-      <c r="A307" s="12" t="inlineStr">
+      <c r="A307" s="21" t="inlineStr">
         <is>
           <t>POSTAL BALLOT VOTES</t>
         </is>
       </c>
       <c r="B307" s="13" t="inlineStr"/>
-      <c r="C307" s="14" t="n">
+      <c r="C307" s="20" t="n">
         <v>330</v>
       </c>
-      <c r="D307" s="14" t="n">
+      <c r="D307" s="20" t="n">
         <v>32</v>
       </c>
-      <c r="E307" s="14" t="n">
+      <c r="E307" s="20" t="n">
         <v>13</v>
       </c>
-      <c r="F307" s="14" t="n">
+      <c r="F307" s="20" t="n">
         <v>341</v>
       </c>
-      <c r="G307" s="14" t="n">
+      <c r="G307" s="20" t="n">
         <v>18</v>
       </c>
-      <c r="H307" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="I307" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="J307" s="14" t="n">
-        <v>1</v>
-      </c>
-      <c r="K307" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="L307" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="M307" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="N307" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="O307" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="P307" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q307" s="14" t="n">
-        <v>1</v>
-      </c>
-      <c r="R307" s="14" t="n">
-        <v>1</v>
-      </c>
-      <c r="S307" s="14" t="n">
+      <c r="H307" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="I307" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="J307" s="20" t="n">
+        <v>1</v>
+      </c>
+      <c r="K307" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="L307" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="M307" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="N307" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="O307" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="P307" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q307" s="20" t="n">
+        <v>1</v>
+      </c>
+      <c r="R307" s="20" t="n">
+        <v>1</v>
+      </c>
+      <c r="S307" s="20" t="n">
         <v>737</v>
       </c>
-      <c r="T307" s="14" t="n">
+      <c r="T307" s="20" t="n">
         <v>22</v>
       </c>
-      <c r="U307" s="14" t="n">
+      <c r="U307" s="20" t="n">
         <v>7</v>
       </c>
-      <c r="V307" s="14" t="n">
+      <c r="V307" s="20" t="n">
         <v>766</v>
       </c>
-      <c r="W307" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="X307" s="14" t="n">
+      <c r="W307" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="X307" s="20" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="308">
-      <c r="A308" s="15" t="inlineStr">
+      <c r="A308" s="22" t="inlineStr">
         <is>
           <t>TOTAL VOTES POLLED</t>
         </is>
       </c>
-      <c r="B308" s="16" t="inlineStr"/>
-      <c r="C308" s="17">
+      <c r="B308" s="23" t="inlineStr"/>
+      <c r="C308" s="24">
         <f>C306+C307</f>
         <v/>
       </c>
-      <c r="D308" s="17">
+      <c r="D308" s="24">
         <f>D306+D307</f>
         <v/>
       </c>
-      <c r="E308" s="17">
+      <c r="E308" s="24">
         <f>E306+E307</f>
         <v/>
       </c>
-      <c r="F308" s="17">
+      <c r="F308" s="24">
         <f>F306+F307</f>
         <v/>
       </c>
-      <c r="G308" s="17">
+      <c r="G308" s="24">
         <f>G306+G307</f>
         <v/>
       </c>
-      <c r="H308" s="17">
+      <c r="H308" s="24">
         <f>H306+H307</f>
         <v/>
       </c>
-      <c r="I308" s="17">
+      <c r="I308" s="24">
         <f>I306+I307</f>
         <v/>
       </c>
-      <c r="J308" s="17">
+      <c r="J308" s="24">
         <f>J306+J307</f>
         <v/>
       </c>
-      <c r="K308" s="17">
+      <c r="K308" s="24">
         <f>K306+K307</f>
         <v/>
       </c>
-      <c r="L308" s="17">
+      <c r="L308" s="24">
         <f>L306+L307</f>
         <v/>
       </c>
-      <c r="M308" s="17">
+      <c r="M308" s="24">
         <f>M306+M307</f>
         <v/>
       </c>
-      <c r="N308" s="17">
+      <c r="N308" s="24">
         <f>N306+N307</f>
         <v/>
       </c>
-      <c r="O308" s="17">
+      <c r="O308" s="24">
         <f>O306+O307</f>
         <v/>
       </c>
-      <c r="P308" s="17">
+      <c r="P308" s="24">
         <f>P306+P307</f>
         <v/>
       </c>
-      <c r="Q308" s="17">
+      <c r="Q308" s="24">
         <f>Q306+Q307</f>
         <v/>
       </c>
-      <c r="R308" s="17">
+      <c r="R308" s="24">
         <f>R306+R307</f>
         <v/>
       </c>
-      <c r="S308" s="17">
+      <c r="S308" s="24">
         <f>S306+S307</f>
         <v/>
       </c>
-      <c r="T308" s="17">
+      <c r="T308" s="24">
         <f>T306+T307</f>
         <v/>
       </c>
-      <c r="U308" s="17">
+      <c r="U308" s="24">
         <f>U306+U307</f>
         <v/>
       </c>
-      <c r="V308" s="17">
+      <c r="V308" s="24">
         <f>V306+V307</f>
         <v/>
       </c>
-      <c r="W308" s="17">
+      <c r="W308" s="24">
         <f>W306+W307</f>
         <v/>
       </c>
-      <c r="X308" s="17">
+      <c r="X308" s="24">
         <f>X306+X307</f>
         <v/>
       </c>
